--- a/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
+++ b/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcadMASTER\environment\runtimefiles\AllCPU-AllOS\zcadelectrotech\data\preload\xlsxtemplates\modelinxlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcad\cad\data\preload\xlsxtemplates\modelinxlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911C70B1-2494-488E-86D5-952C10AF7F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E42F043-C78E-4299-85AC-A5237A99185D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="2445" windowWidth="40725" windowHeight="17940" tabRatio="643" activeTab="4" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
+    <workbookView xWindow="19920" yWindow="1260" windowWidth="29070" windowHeight="19290" tabRatio="643" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="4" r:id="rId1"/>
@@ -37,17 +37,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -783,14 +772,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -805,7 +794,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="666">
   <si>
     <t>&lt;zlight&gt;</t>
   </si>
@@ -1697,9 +1686,6 @@
     <t>С</t>
   </si>
   <si>
-    <t>Тип защитной характеристики</t>
-  </si>
-  <si>
     <t>IP54</t>
   </si>
   <si>
@@ -1709,9 +1695,6 @@
     <t>Коэффициент мощности, cosf</t>
   </si>
   <si>
-    <t>Предел коммутац. стойкость,кА</t>
-  </si>
-  <si>
     <t>Навесное</t>
   </si>
   <si>
@@ -1719,9 +1702,6 @@
   </si>
   <si>
     <t>Ток от установленной мощности, А</t>
-  </si>
-  <si>
-    <t>Уставка расцепителя,А</t>
   </si>
   <si>
     <t>Артикул/код щита</t>
@@ -2689,12 +2669,6 @@
     <t>UUVEL_SOCKET_1P54IN</t>
   </si>
   <si>
-    <t>ВА 47-63</t>
-  </si>
-  <si>
-    <t>АВДТ-63</t>
-  </si>
-  <si>
     <t>Оределяем уникальность прокладки</t>
   </si>
   <si>
@@ -2768,6 +2742,69 @@
   </si>
   <si>
     <t>скр. в мет.тр.</t>
+  </si>
+  <si>
+    <t>Позиция</t>
+  </si>
+  <si>
+    <t>Марка автомата</t>
+  </si>
+  <si>
+    <t>NMO_BaseName</t>
+  </si>
+  <si>
+    <t>NMO_Prefix</t>
+  </si>
+  <si>
+    <t>NMO_Suffix</t>
+  </si>
+  <si>
+    <t>VSPECIFICATION_Brand</t>
+  </si>
+  <si>
+    <t>Схема</t>
+  </si>
+  <si>
+    <t>VEL_POWER_CABLEOUT</t>
+  </si>
+  <si>
+    <t>UUVEL_POWER_CABLEOUT</t>
+  </si>
+  <si>
+    <t>VEL_SOCKET_1P54OUT</t>
+  </si>
+  <si>
+    <t>UUVEL_SOCKET_1P54OUT</t>
+  </si>
+  <si>
+    <t>VEL_SOCKET_3F54OUT</t>
+  </si>
+  <si>
+    <t>UUVEL_SOCKET_3F54OUT</t>
+  </si>
+  <si>
+    <t>VEL_SOCKET_3P54OUT</t>
+  </si>
+  <si>
+    <t>UUVEL_SOCKET_3P54OUT</t>
+  </si>
+  <si>
+    <t>ВА 47-60</t>
+  </si>
+  <si>
+    <t>ВА 47-100</t>
+  </si>
+  <si>
+    <t>ВА88-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВА88-35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВА88-37 </t>
+  </si>
+  <si>
+    <t>АВДТ32</t>
   </si>
 </sst>
 </file>
@@ -2778,7 +2815,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3057,8 +3094,20 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF993300"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="69">
+  <fills count="70">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3464,6 +3513,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -4161,12 +4216,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4850,6 +4906,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="56" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="69" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4906,9 +5058,6 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5000,113 +5149,40 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 28" xfId="3" xr:uid="{C0335F02-4580-4C3D-AA3E-A2D2FCB3FB52}"/>
     <cellStyle name="Обычный 4" xfId="2" xr:uid="{48E5EE6E-1ABC-45BC-BBF9-DFA8FA4F7CCC}"/>
     <cellStyle name="Обычный_расчет нагрузки" xfId="1" xr:uid="{2A78680A-EF87-4AAC-8D9D-BEC6B0A95A74}"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="50">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC89D7D"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC89D7D"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5120,49 +5196,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5211,7 +5245,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5225,7 +5259,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5239,7 +5287,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5253,7 +5315,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5267,7 +5350,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5281,14 +5378,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5480,9 +5577,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5520,7 +5617,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5626,7 +5723,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5768,7 +5865,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5790,87 +5887,87 @@
   <sheetData>
     <row r="2" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:79" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="271" t="s">
+      <c r="A3" s="232" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="272"/>
-      <c r="C3" s="273"/>
-      <c r="F3" s="274" t="s">
+      <c r="B3" s="233"/>
+      <c r="C3" s="234"/>
+      <c r="F3" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="275"/>
-      <c r="H3" s="276"/>
-      <c r="K3" s="269" t="s">
+      <c r="G3" s="236"/>
+      <c r="H3" s="237"/>
+      <c r="K3" s="230" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="270"/>
-      <c r="M3" s="270"/>
-      <c r="N3" s="270"/>
-      <c r="O3" s="270"/>
-      <c r="P3" s="270"/>
-      <c r="Q3" s="270"/>
-      <c r="R3" s="270"/>
-      <c r="S3" s="270"/>
-      <c r="T3" s="270"/>
-      <c r="U3" s="270"/>
-      <c r="V3" s="270"/>
-      <c r="W3" s="270"/>
-      <c r="X3" s="270"/>
-      <c r="Y3" s="270"/>
-      <c r="Z3" s="270"/>
-      <c r="AA3" s="270"/>
-      <c r="AB3" s="270"/>
-      <c r="AC3" s="270"/>
-      <c r="AD3" s="270"/>
-      <c r="AE3" s="270"/>
-      <c r="AF3" s="270"/>
-      <c r="AG3" s="270"/>
-      <c r="AH3" s="270"/>
-      <c r="AI3" s="270"/>
-      <c r="AJ3" s="270"/>
-      <c r="AK3" s="270"/>
-      <c r="AL3" s="270"/>
-      <c r="AM3" s="270"/>
-      <c r="AN3" s="270"/>
-      <c r="AO3" s="270"/>
-      <c r="AP3" s="270"/>
-      <c r="AQ3" s="270"/>
-      <c r="AR3" s="270"/>
-      <c r="AS3" s="270"/>
-      <c r="AT3" s="270"/>
-      <c r="AU3" s="270"/>
-      <c r="AV3" s="270"/>
-      <c r="AW3" s="270"/>
-      <c r="AX3" s="270"/>
-      <c r="AY3" s="270"/>
-      <c r="AZ3" s="270"/>
-      <c r="BA3" s="270"/>
-      <c r="BB3" s="270"/>
-      <c r="BC3" s="270"/>
-      <c r="BD3" s="270"/>
-      <c r="BE3" s="270"/>
-      <c r="BF3" s="270"/>
-      <c r="BG3" s="270"/>
-      <c r="BH3" s="270"/>
-      <c r="BI3" s="270"/>
-      <c r="BJ3" s="270"/>
-      <c r="BK3" s="270"/>
-      <c r="BL3" s="270"/>
-      <c r="BM3" s="270"/>
-      <c r="BN3" s="270"/>
-      <c r="BO3" s="270"/>
-      <c r="BP3" s="270"/>
-      <c r="BQ3" s="270"/>
-      <c r="BR3" s="270"/>
-      <c r="BS3" s="270"/>
-      <c r="BT3" s="270"/>
-      <c r="BU3" s="270"/>
-      <c r="BV3" s="270"/>
-      <c r="BW3" s="270"/>
-      <c r="BX3" s="270"/>
-      <c r="BY3" s="270"/>
-      <c r="BZ3" s="270"/>
-      <c r="CA3" s="270"/>
+      <c r="L3" s="231"/>
+      <c r="M3" s="231"/>
+      <c r="N3" s="231"/>
+      <c r="O3" s="231"/>
+      <c r="P3" s="231"/>
+      <c r="Q3" s="231"/>
+      <c r="R3" s="231"/>
+      <c r="S3" s="231"/>
+      <c r="T3" s="231"/>
+      <c r="U3" s="231"/>
+      <c r="V3" s="231"/>
+      <c r="W3" s="231"/>
+      <c r="X3" s="231"/>
+      <c r="Y3" s="231"/>
+      <c r="Z3" s="231"/>
+      <c r="AA3" s="231"/>
+      <c r="AB3" s="231"/>
+      <c r="AC3" s="231"/>
+      <c r="AD3" s="231"/>
+      <c r="AE3" s="231"/>
+      <c r="AF3" s="231"/>
+      <c r="AG3" s="231"/>
+      <c r="AH3" s="231"/>
+      <c r="AI3" s="231"/>
+      <c r="AJ3" s="231"/>
+      <c r="AK3" s="231"/>
+      <c r="AL3" s="231"/>
+      <c r="AM3" s="231"/>
+      <c r="AN3" s="231"/>
+      <c r="AO3" s="231"/>
+      <c r="AP3" s="231"/>
+      <c r="AQ3" s="231"/>
+      <c r="AR3" s="231"/>
+      <c r="AS3" s="231"/>
+      <c r="AT3" s="231"/>
+      <c r="AU3" s="231"/>
+      <c r="AV3" s="231"/>
+      <c r="AW3" s="231"/>
+      <c r="AX3" s="231"/>
+      <c r="AY3" s="231"/>
+      <c r="AZ3" s="231"/>
+      <c r="BA3" s="231"/>
+      <c r="BB3" s="231"/>
+      <c r="BC3" s="231"/>
+      <c r="BD3" s="231"/>
+      <c r="BE3" s="231"/>
+      <c r="BF3" s="231"/>
+      <c r="BG3" s="231"/>
+      <c r="BH3" s="231"/>
+      <c r="BI3" s="231"/>
+      <c r="BJ3" s="231"/>
+      <c r="BK3" s="231"/>
+      <c r="BL3" s="231"/>
+      <c r="BM3" s="231"/>
+      <c r="BN3" s="231"/>
+      <c r="BO3" s="231"/>
+      <c r="BP3" s="231"/>
+      <c r="BQ3" s="231"/>
+      <c r="BR3" s="231"/>
+      <c r="BS3" s="231"/>
+      <c r="BT3" s="231"/>
+      <c r="BU3" s="231"/>
+      <c r="BV3" s="231"/>
+      <c r="BW3" s="231"/>
+      <c r="BX3" s="231"/>
+      <c r="BY3" s="231"/>
+      <c r="BZ3" s="231"/>
+      <c r="CA3" s="231"/>
     </row>
     <row r="4" spans="1:79" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -6025,13 +6122,13 @@
         <v>138</v>
       </c>
       <c r="BC4" s="213" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="BD4" s="213" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="BE4" s="213" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="BF4" s="43" t="s">
         <v>89</v>
@@ -6469,7 +6566,7 @@
         <v>127</v>
       </c>
       <c r="AI6" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ6" s="2">
         <v>0</v>
@@ -6518,14 +6615,14 @@
         <v>129</v>
       </c>
       <c r="AZ6" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA6" s="2"/>
       <c r="BB6" s="2">
         <v>5</v>
       </c>
       <c r="BC6" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD6" s="210">
         <v>12.5</v>
@@ -6669,7 +6766,7 @@
         <v>127</v>
       </c>
       <c r="AI7" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ7" s="2">
         <v>0</v>
@@ -6718,14 +6815,14 @@
         <v>129</v>
       </c>
       <c r="AZ7" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA7" s="2"/>
       <c r="BB7" s="2">
         <v>5</v>
       </c>
       <c r="BC7" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD7" s="210">
         <v>12.5</v>
@@ -6870,7 +6967,7 @@
         <v>127</v>
       </c>
       <c r="AI8" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ8" s="2">
         <v>0</v>
@@ -6919,14 +7016,14 @@
         <v>129</v>
       </c>
       <c r="AZ8" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA8" s="2"/>
       <c r="BB8" s="2">
         <v>5</v>
       </c>
       <c r="BC8" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD8" s="210">
         <v>12.5</v>
@@ -6989,10 +7086,10 @@
       <c r="CA8" s="2"/>
     </row>
     <row r="9" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="277" t="s">
+      <c r="A9" s="238" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="278"/>
+      <c r="B9" s="239"/>
       <c r="F9" s="27">
         <v>2500</v>
       </c>
@@ -7069,7 +7166,7 @@
         <v>127</v>
       </c>
       <c r="AI9" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ9" s="2">
         <v>0</v>
@@ -7118,14 +7215,14 @@
         <v>129</v>
       </c>
       <c r="AZ9" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA9" s="2"/>
       <c r="BB9" s="2">
         <v>5</v>
       </c>
       <c r="BC9" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD9" s="210">
         <v>12.5</v>
@@ -7270,7 +7367,7 @@
         <v>127</v>
       </c>
       <c r="AI10" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ10" s="2">
         <v>0</v>
@@ -7319,14 +7416,14 @@
         <v>129</v>
       </c>
       <c r="AZ10" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA10" s="2"/>
       <c r="BB10" s="2">
         <v>5</v>
       </c>
       <c r="BC10" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD10" s="210">
         <v>12.5</v>
@@ -7471,7 +7568,7 @@
         <v>127</v>
       </c>
       <c r="AI11" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ11" s="2">
         <v>0</v>
@@ -7520,14 +7617,14 @@
         <v>129</v>
       </c>
       <c r="AZ11" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA11" s="2"/>
       <c r="BB11" s="2">
         <v>5</v>
       </c>
       <c r="BC11" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD11" s="210">
         <v>12.5</v>
@@ -7672,7 +7769,7 @@
         <v>127</v>
       </c>
       <c r="AI12" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ12" s="2">
         <v>0</v>
@@ -7721,14 +7818,14 @@
         <v>129</v>
       </c>
       <c r="AZ12" s="210" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="BA12" s="2"/>
       <c r="BB12" s="2">
         <v>5</v>
       </c>
       <c r="BC12" s="210" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="BD12" s="210">
         <v>12.5</v>
@@ -7867,7 +7964,7 @@
         <v>127</v>
       </c>
       <c r="AI13" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ13" s="2">
         <v>0</v>
@@ -8044,7 +8141,7 @@
         <v>127</v>
       </c>
       <c r="AI14" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ14" s="2">
         <v>0</v>
@@ -8215,7 +8312,7 @@
         <v>127</v>
       </c>
       <c r="AI15" s="210" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
       <c r="AJ15" s="2">
         <v>0</v>
@@ -8495,7 +8592,7 @@
         <v>0.255</v>
       </c>
       <c r="K17" s="2">
-        <v>400</v>
+        <v>315</v>
       </c>
       <c r="L17" s="2">
         <v>0.65</v>
@@ -8506,7 +8603,9 @@
       <c r="N17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O17" s="2"/>
+      <c r="O17" s="228" t="s">
+        <v>664</v>
+      </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2">
         <v>2</v>
@@ -8675,7 +8774,9 @@
       <c r="N18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O18" s="2"/>
+      <c r="O18" s="228" t="s">
+        <v>664</v>
+      </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2">
         <v>2</v>
@@ -8844,7 +8945,9 @@
       <c r="N19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" s="228" t="s">
+        <v>663</v>
+      </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2">
         <v>2</v>
@@ -9013,7 +9116,9 @@
       <c r="N20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="O20" s="228" t="s">
+        <v>663</v>
+      </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2">
         <v>2</v>
@@ -9182,7 +9287,9 @@
       <c r="N21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O21" s="2"/>
+      <c r="O21" s="228" t="s">
+        <v>662</v>
+      </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2">
         <v>2</v>
@@ -9351,7 +9458,9 @@
       <c r="N22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O22" s="2"/>
+      <c r="O22" s="210" t="s">
+        <v>661</v>
+      </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2">
         <v>2</v>
@@ -9516,7 +9625,9 @@
       <c r="N23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O23" s="2"/>
+      <c r="O23" s="210" t="s">
+        <v>661</v>
+      </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2">
         <v>2</v>
@@ -9682,7 +9793,7 @@
         <v>101</v>
       </c>
       <c r="O24" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2">
@@ -9849,7 +9960,7 @@
         <v>101</v>
       </c>
       <c r="O25" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2">
@@ -10016,7 +10127,7 @@
         <v>101</v>
       </c>
       <c r="O26" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2">
@@ -10183,7 +10294,7 @@
         <v>101</v>
       </c>
       <c r="O27" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2">
@@ -10350,7 +10461,7 @@
         <v>101</v>
       </c>
       <c r="O28" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2">
@@ -10517,7 +10628,7 @@
         <v>101</v>
       </c>
       <c r="O29" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2">
@@ -10684,7 +10795,7 @@
         <v>101</v>
       </c>
       <c r="O30" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2">
@@ -10851,7 +10962,7 @@
         <v>101</v>
       </c>
       <c r="O31" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2">
@@ -11018,7 +11129,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2">
@@ -11185,7 +11296,7 @@
         <v>101</v>
       </c>
       <c r="O33" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2">
@@ -11352,7 +11463,7 @@
         <v>101</v>
       </c>
       <c r="O34" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2">
@@ -11519,7 +11630,7 @@
         <v>101</v>
       </c>
       <c r="O35" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2">
@@ -11686,7 +11797,7 @@
         <v>101</v>
       </c>
       <c r="O36" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2">
@@ -11844,7 +11955,7 @@
         <v>101</v>
       </c>
       <c r="O37" s="210" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2">
@@ -12125,15 +12236,15 @@
     </row>
     <row r="41" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F42" s="274" t="s">
+      <c r="F42" s="235" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="275"/>
-      <c r="H42" s="276"/>
-      <c r="K42" s="279" t="s">
-        <v>503</v>
-      </c>
-      <c r="L42" s="280"/>
+      <c r="G42" s="236"/>
+      <c r="H42" s="237"/>
+      <c r="K42" s="240" t="s">
+        <v>500</v>
+      </c>
+      <c r="L42" s="241"/>
     </row>
     <row r="43" spans="6:79" ht="31.5" x14ac:dyDescent="0.25">
       <c r="F43" s="36" t="s">
@@ -12146,7 +12257,7 @@
         <v>22</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="L43" s="2">
         <v>1</v>
@@ -12159,7 +12270,7 @@
       <c r="G44" s="28"/>
       <c r="H44" s="29"/>
       <c r="K44" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="L44" s="2">
         <v>0</v>
@@ -12172,7 +12283,7 @@
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
       <c r="K45" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L45" s="2">
         <v>1</v>
@@ -12185,7 +12296,7 @@
       <c r="G46" s="28"/>
       <c r="H46" s="29"/>
       <c r="K46" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L46" s="2">
         <v>0</v>
@@ -12198,7 +12309,7 @@
       <c r="G47" s="28"/>
       <c r="H47" s="29"/>
       <c r="K47" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="L47" s="2">
         <v>0</v>
@@ -12226,14 +12337,14 @@
       <c r="H50" s="29"/>
     </row>
     <row r="56" spans="3:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="268" t="s">
-        <v>611</v>
-      </c>
-      <c r="D56" s="268"/>
+      <c r="C56" s="229" t="s">
+        <v>608</v>
+      </c>
+      <c r="D56" s="229"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -12241,7 +12352,7 @@
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -12249,26 +12360,26 @@
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C59" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C60" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -12283,77 +12394,87 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="K6:M38">
-    <cfRule type="cellIs" dxfId="47" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="29" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N6:T23 N24:N37 P24:T37">
-    <cfRule type="cellIs" dxfId="46" priority="24" operator="equal">
+  <conditionalFormatting sqref="N6:T21 N22:N37 P22:T37">
+    <cfRule type="cellIs" dxfId="48" priority="26" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N38:AG38">
-    <cfRule type="cellIs" dxfId="45" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="25" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O24:O37">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:X12">
-    <cfRule type="cellIs" dxfId="43" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:AA6 BF6:BJ6 BA6:BB12 BM6:BU37 Y7:Z12 BF7:BK12 AA7:AA37 U13:Z37 AO13:BK37">
-    <cfRule type="cellIs" dxfId="42" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="30" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB6:AG37">
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH6:AH38">
+    <cfRule type="cellIs" dxfId="42" priority="21" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI6:AI15">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI16:AI38">
     <cfRule type="cellIs" dxfId="40" priority="19" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI6:AI15">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AI38">
-    <cfRule type="cellIs" dxfId="38" priority="17" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AJ6:AN37">
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ38:BU38">
-    <cfRule type="cellIs" dxfId="36" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="23" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO6:AY12">
-    <cfRule type="cellIs" dxfId="35" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC6:BE12">
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV6:CA38">
-    <cfRule type="cellIs" dxfId="33" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="10" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O23">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O22">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12414,7 +12535,7 @@
         <v>170</v>
       </c>
       <c r="B1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -12422,7 +12543,7 @@
         <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12430,7 +12551,7 @@
         <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -12438,7 +12559,7 @@
         <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12446,7 +12567,7 @@
         <v>170</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -12454,7 +12575,7 @@
         <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -12551,34 +12672,34 @@
     </row>
     <row r="3" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="C3" s="61"/>
-      <c r="D3" s="288" t="s">
+      <c r="D3" s="249" t="s">
+        <v>328</v>
+      </c>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="249" t="s">
+        <v>329</v>
+      </c>
+      <c r="H3" s="249"/>
+      <c r="I3" s="249"/>
+      <c r="J3" s="70" t="s">
+        <v>332</v>
+      </c>
+      <c r="K3" s="70" t="s">
+        <v>330</v>
+      </c>
+      <c r="L3" s="249" t="s">
         <v>331</v>
       </c>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="288" t="s">
-        <v>332</v>
-      </c>
-      <c r="H3" s="288"/>
-      <c r="I3" s="288"/>
-      <c r="J3" s="70" t="s">
-        <v>335</v>
-      </c>
-      <c r="K3" s="70" t="s">
-        <v>333</v>
-      </c>
-      <c r="L3" s="288" t="s">
-        <v>334</v>
-      </c>
-      <c r="M3" s="288"/>
-      <c r="N3" s="288"/>
-      <c r="O3" s="291" t="s">
-        <v>342</v>
-      </c>
-      <c r="P3" s="291"/>
-      <c r="Q3" s="291"/>
+      <c r="M3" s="249"/>
+      <c r="N3" s="249"/>
+      <c r="O3" s="253" t="s">
+        <v>339</v>
+      </c>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
       <c r="R3" s="76" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -12652,28 +12773,28 @@
         <v>142</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E6" s="48"/>
       <c r="F6" s="49"/>
       <c r="G6" s="50" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H6" s="48"/>
       <c r="I6" s="49"/>
       <c r="J6" s="48" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K6" s="48" t="s">
+        <v>334</v>
+      </c>
+      <c r="L6" s="50" t="s">
         <v>337</v>
-      </c>
-      <c r="L6" s="50" t="s">
-        <v>340</v>
       </c>
       <c r="M6" s="48"/>
       <c r="N6" s="49"/>
       <c r="O6" s="50" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="P6" s="48"/>
       <c r="Q6" s="49"/>
@@ -12826,82 +12947,82 @@
       <c r="B5" s="59"/>
       <c r="C5" s="59"/>
       <c r="D5" s="116" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" s="116" t="s">
+        <v>329</v>
+      </c>
+      <c r="F5" s="116" t="s">
+        <v>330</v>
+      </c>
+      <c r="G5" s="116" t="s">
+        <v>339</v>
+      </c>
+      <c r="H5" s="116" t="s">
         <v>331</v>
       </c>
-      <c r="E5" s="116" t="s">
-        <v>332</v>
-      </c>
-      <c r="F5" s="116" t="s">
-        <v>333</v>
-      </c>
-      <c r="G5" s="116" t="s">
-        <v>342</v>
-      </c>
-      <c r="H5" s="116" t="s">
-        <v>334</v>
-      </c>
       <c r="I5" s="116" t="s">
+        <v>344</v>
+      </c>
+      <c r="J5" s="116" t="s">
+        <v>345</v>
+      </c>
+      <c r="K5" s="116" t="s">
+        <v>346</v>
+      </c>
+      <c r="L5" s="116" t="s">
         <v>347</v>
       </c>
-      <c r="J5" s="116" t="s">
+      <c r="M5" s="116" t="s">
         <v>348</v>
       </c>
-      <c r="K5" s="116" t="s">
+      <c r="N5" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="L5" s="116" t="s">
+      <c r="O5" s="116" t="s">
         <v>350</v>
       </c>
-      <c r="M5" s="116" t="s">
+      <c r="P5" s="116" t="s">
         <v>351</v>
       </c>
-      <c r="N5" s="116" t="s">
+      <c r="Q5" s="76" t="s">
         <v>352</v>
       </c>
-      <c r="O5" s="116" t="s">
+      <c r="R5" s="116" t="s">
         <v>353</v>
       </c>
-      <c r="P5" s="116" t="s">
+      <c r="S5" s="116" t="s">
         <v>354</v>
       </c>
-      <c r="Q5" s="76" t="s">
+      <c r="T5" s="116" t="s">
         <v>355</v>
       </c>
-      <c r="R5" s="116" t="s">
+      <c r="U5" s="116" t="s">
         <v>356</v>
       </c>
-      <c r="S5" s="116" t="s">
+      <c r="V5" s="116" t="s">
+        <v>339</v>
+      </c>
+      <c r="W5" s="116" t="s">
         <v>357</v>
       </c>
-      <c r="T5" s="116" t="s">
-        <v>358</v>
-      </c>
-      <c r="U5" s="116" t="s">
-        <v>359</v>
-      </c>
-      <c r="V5" s="116" t="s">
-        <v>342</v>
-      </c>
-      <c r="W5" s="116" t="s">
-        <v>360</v>
-      </c>
       <c r="X5" s="117" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Y5" s="118" t="s">
+        <v>482</v>
+      </c>
+      <c r="Z5" s="118" t="s">
+        <v>483</v>
+      </c>
+      <c r="AA5" s="119" t="s">
+        <v>484</v>
+      </c>
+      <c r="AB5" s="119" t="s">
         <v>485</v>
       </c>
-      <c r="Z5" s="118" t="s">
-        <v>486</v>
-      </c>
-      <c r="AA5" s="119" t="s">
-        <v>487</v>
-      </c>
-      <c r="AB5" s="119" t="s">
-        <v>488</v>
-      </c>
       <c r="AC5" s="215" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="AD5" s="59"/>
     </row>
@@ -12940,7 +13061,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B7" s="59" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C7" s="59" t="str">
         <f>IF(COUNTIF($B$7:B7,B7)=1,"&lt;zzzimport&gt;",1)</f>
@@ -13061,24 +13182,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="C1" s="241" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="241"/>
-      <c r="L1" s="292" t="s">
-        <v>469</v>
-      </c>
-      <c r="M1" s="292"/>
-      <c r="N1" s="292"/>
-      <c r="O1" s="292"/>
-      <c r="P1" s="292"/>
-      <c r="Q1" s="292"/>
-      <c r="R1" s="292"/>
-      <c r="S1" s="292"/>
+      <c r="C1" s="252" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1" s="252"/>
+      <c r="L1" s="254" t="s">
+        <v>466</v>
+      </c>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="254"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="254"/>
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C2" s="97" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D2" s="97">
         <v>1</v>
@@ -13086,26 +13207,26 @@
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C3" s="97" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D3" s="97">
         <f>D2</f>
         <v>1</v>
       </c>
       <c r="N3" t="s">
+        <v>467</v>
+      </c>
+      <c r="O3" t="s">
+        <v>468</v>
+      </c>
+      <c r="P3" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q3" t="s">
         <v>470</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>471</v>
-      </c>
-      <c r="P3" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>473</v>
-      </c>
-      <c r="R3" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="4" spans="2:45" x14ac:dyDescent="0.25">
@@ -13113,7 +13234,7 @@
         <v>209</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="N4" s="126">
         <v>0</v>
@@ -13138,28 +13259,28 @@
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>165</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>231</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K6" s="102" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N6" s="129"/>
       <c r="O6" s="126">
@@ -13172,7 +13293,7 @@
     </row>
     <row r="7" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C7" s="1">
         <f>'&lt;zallcab&gt;CALC'!S7</f>
@@ -13209,7 +13330,7 @@
         <v>209</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N7" s="129">
         <v>0</v>
@@ -13230,49 +13351,49 @@
         <v>0</v>
       </c>
       <c r="S7" s="130" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="T7" s="115" t="str">
         <f>IF(C7=0,"",C7)</f>
         <v/>
       </c>
       <c r="U7" s="131" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="V7" s="131" t="str">
         <f>IF(C7=0,"",D7)</f>
         <v/>
       </c>
       <c r="W7" s="132" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="X7" s="133" t="str">
         <f>IF(C7=0,"",E7)</f>
         <v/>
       </c>
       <c r="Y7" s="132" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="Z7" s="131" t="str">
         <f>IF(C7=0,"",F7)</f>
         <v/>
       </c>
       <c r="AA7" s="134" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AB7" s="135" t="str">
         <f>IF(C7=0,"",G7)</f>
         <v/>
       </c>
       <c r="AC7" s="136" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AD7" s="135" t="str">
         <f>IF(C7=0,"",H7)</f>
         <v/>
       </c>
       <c r="AE7" s="136" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AF7" s="137" t="str">
         <f>IF(C7=0,"",I7)</f>
@@ -13310,14 +13431,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C1" s="241" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="241"/>
+      <c r="C1" s="252" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1" s="252"/>
     </row>
     <row r="2" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C2" s="97" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D2" s="97">
         <v>1</v>
@@ -13325,7 +13446,7 @@
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C3" s="97" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D3" s="97">
         <f>D2</f>
@@ -13334,18 +13455,18 @@
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C7" s="1">
         <f>'&lt;zallcab&gt;CALC'!D7</f>
@@ -13444,7 +13565,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -13452,7 +13573,7 @@
         <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -13465,12 +13586,12 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B6" t="s">
         <v>0</v>
@@ -13481,7 +13602,7 @@
         <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -13516,7 +13637,7 @@
         <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -13541,7 +13662,7 @@
         <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -13636,7 +13757,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>165</v>
@@ -13648,23 +13769,23 @@
         <v>7</v>
       </c>
       <c r="I5" s="70" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J5" s="70" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K5" s="70" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L5" s="74"/>
       <c r="M5" s="74"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D6" s="48">
         <f>'&lt;zalldev&gt;EXPORT'!D11</f>
@@ -13698,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M6" t="s">
         <v>189</v>
@@ -13711,7 +13832,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B9844E-F661-46DB-A8DF-606C0C725DFB}">
-  <dimension ref="A1:JD28"/>
+  <dimension ref="A1:JV28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2.7109375" customWidth="1"/>
@@ -13719,7 +13840,7 @@
     <col min="5" max="7" width="7.7109375" customWidth="1"/>
     <col min="8" max="8" width="40.7109375" customWidth="1"/>
     <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
     <col min="11" max="11" width="35.7109375" customWidth="1"/>
     <col min="12" max="14" width="7.7109375" customWidth="1"/>
     <col min="15" max="15" width="25.7109375" customWidth="1"/>
@@ -13741,6 +13862,7 @@
     <col min="110" max="171" width="7.7109375" customWidth="1"/>
     <col min="172" max="174" width="9" customWidth="1"/>
     <col min="197" max="197" width="11" customWidth="1"/>
+    <col min="267" max="267" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:57" x14ac:dyDescent="0.25">
@@ -13752,9 +13874,9 @@
         <f ca="1">U6</f>
         <v>0</v>
       </c>
-      <c r="F1" s="1">
-        <f>U8</f>
-        <v>0.92</v>
+      <c r="F1" s="1" t="e">
+        <f ca="1">U8</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="G1" s="1">
         <f>H11</f>
@@ -13766,36 +13888,36 @@
       </c>
     </row>
     <row r="4" spans="4:57" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="226" t="s">
-        <v>313</v>
-      </c>
-      <c r="E4" s="226"/>
-      <c r="F4" s="226"/>
-      <c r="G4" s="226"/>
-      <c r="H4" s="226"/>
+      <c r="D4" s="259" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
       <c r="I4" s="62" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J4" s="89"/>
       <c r="K4" s="89"/>
       <c r="P4" s="62"/>
-      <c r="Q4" s="226" t="s">
-        <v>311</v>
-      </c>
-      <c r="R4" s="226"/>
-      <c r="S4" s="226"/>
-      <c r="T4" s="226"/>
-      <c r="U4" s="226"/>
-      <c r="V4" s="226"/>
-      <c r="Z4" s="241" t="s">
-        <v>431</v>
-      </c>
-      <c r="AA4" s="241"/>
+      <c r="Q4" s="259" t="s">
+        <v>308</v>
+      </c>
+      <c r="R4" s="259"/>
+      <c r="S4" s="259"/>
+      <c r="T4" s="259"/>
+      <c r="U4" s="259"/>
+      <c r="V4" s="259"/>
+      <c r="Z4" s="252" t="s">
+        <v>428</v>
+      </c>
+      <c r="AA4" s="252"/>
       <c r="AU4" s="94" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AV4" s="94" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AW4" s="94"/>
       <c r="AX4" s="94" t="s">
@@ -13803,59 +13925,61 @@
       </c>
       <c r="AY4" s="94"/>
       <c r="AZ4" s="94" t="s">
+        <v>394</v>
+      </c>
+      <c r="BA4" s="94" t="s">
+        <v>399</v>
+      </c>
+      <c r="BB4" s="94" t="s">
+        <v>393</v>
+      </c>
+      <c r="BC4" s="94" t="s">
         <v>397</v>
       </c>
-      <c r="BA4" s="94" t="s">
-        <v>402</v>
-      </c>
-      <c r="BB4" s="94" t="s">
-        <v>396</v>
-      </c>
-      <c r="BC4" s="94" t="s">
+      <c r="BD4" s="94" t="s">
         <v>400</v>
       </c>
-      <c r="BD4" s="94" t="s">
-        <v>403</v>
-      </c>
     </row>
     <row r="5" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D5" s="227" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
+      <c r="D5" s="260" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
       <c r="H5" s="98">
         <f>AU5</f>
         <v>0</v>
       </c>
-      <c r="I5" s="61" t="s">
-        <v>309</v>
-      </c>
-      <c r="J5" s="90"/>
+      <c r="I5" s="225" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="224" t="s">
+        <v>501</v>
+      </c>
       <c r="K5" s="90"/>
       <c r="P5" s="61" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q5" s="228" t="s">
-        <v>307</v>
-      </c>
-      <c r="R5" s="228"/>
-      <c r="S5" s="228"/>
-      <c r="T5" s="228"/>
-      <c r="U5" s="228">
+        <v>305</v>
+      </c>
+      <c r="Q5" s="261" t="s">
+        <v>304</v>
+      </c>
+      <c r="R5" s="261"/>
+      <c r="S5" s="261"/>
+      <c r="T5" s="261"/>
+      <c r="U5" s="261">
         <f ca="1">ROUNDUP(SUM($AC$26:$AC$900000),2)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="228"/>
+      <c r="V5" s="261"/>
       <c r="Z5" s="97" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AA5" s="97">
         <v>1</v>
       </c>
       <c r="AT5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AU5" s="48">
         <f>'&lt;zlight&gt;TEMPGU'!D6</f>
@@ -13896,134 +14020,147 @@
       </c>
     </row>
     <row r="6" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D6" s="229" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
+      <c r="D6" s="262" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="262"/>
       <c r="H6" s="88" t="s">
-        <v>438</v>
-      </c>
-      <c r="I6" s="61" t="s">
-        <v>305</v>
-      </c>
-      <c r="J6" s="90"/>
+        <v>435</v>
+      </c>
+      <c r="I6" s="225" t="s">
+        <v>302</v>
+      </c>
+      <c r="J6" s="226" t="e">
+        <f ca="1">IF(J5="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),MATCH(U15,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),-1)))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K6" s="90"/>
       <c r="P6" s="61">
         <v>63</v>
       </c>
-      <c r="Q6" s="228" t="s">
-        <v>304</v>
-      </c>
-      <c r="R6" s="228"/>
-      <c r="S6" s="228"/>
-      <c r="T6" s="228"/>
-      <c r="U6" s="228">
+      <c r="Q6" s="261" t="s">
+        <v>301</v>
+      </c>
+      <c r="R6" s="261"/>
+      <c r="S6" s="261"/>
+      <c r="T6" s="261"/>
+      <c r="U6" s="261">
         <f ca="1">ROUNDUP(U5*U11,2)</f>
         <v>0</v>
       </c>
-      <c r="V6" s="228"/>
+      <c r="V6" s="261"/>
       <c r="Z6" s="97" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AA6" s="97">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D7" s="222" t="s">
-        <v>303</v>
-      </c>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="222"/>
+      <c r="D7" s="255" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="255"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
       <c r="H7" s="58">
         <v>45399</v>
       </c>
-      <c r="I7" s="61" t="s">
-        <v>302</v>
-      </c>
-      <c r="J7" s="90"/>
+      <c r="I7" s="225" t="s">
+        <v>645</v>
+      </c>
+      <c r="J7" s="226" t="e">
+        <f ca="1">IF(J5="","","1"&amp;INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"О",BD!$K$4:$CB$4,0))),MATCH(J6,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K7" s="90"/>
       <c r="P7" s="61">
         <v>32</v>
       </c>
-      <c r="Q7" s="228" t="s">
-        <v>301</v>
-      </c>
-      <c r="R7" s="228"/>
-      <c r="S7" s="228"/>
-      <c r="T7" s="228"/>
-      <c r="U7" s="228">
+      <c r="Q7" s="261" t="s">
+        <v>299</v>
+      </c>
+      <c r="R7" s="261"/>
+      <c r="S7" s="261"/>
+      <c r="T7" s="261"/>
+      <c r="U7" s="261" t="e">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!C4:C5,MATCH(H11,BD!B4:B5,0))*U8),2)</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="228"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="261"/>
     </row>
     <row r="8" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D8" s="222" t="s">
-        <v>300</v>
-      </c>
-      <c r="E8" s="222"/>
-      <c r="F8" s="222"/>
-      <c r="G8" s="222"/>
+      <c r="D8" s="255" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="255"/>
+      <c r="F8" s="255"/>
+      <c r="G8" s="255"/>
       <c r="H8" s="58" t="s">
-        <v>299</v>
-      </c>
-      <c r="I8" s="61" t="s">
-        <v>298</v>
-      </c>
-      <c r="J8" s="90"/>
+        <v>297</v>
+      </c>
+      <c r="I8" s="225" t="s">
+        <v>646</v>
+      </c>
+      <c r="J8" s="226" t="e">
+        <f ca="1">IF(J5="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"М",BD!$K$4:$CB$4,0))),MATCH(J6,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K8" s="90"/>
       <c r="P8" s="61">
         <v>6</v>
       </c>
-      <c r="Q8" s="230" t="s">
-        <v>297</v>
-      </c>
-      <c r="R8" s="231"/>
-      <c r="S8" s="231"/>
-      <c r="T8" s="232"/>
-      <c r="U8" s="235">
-        <v>0.92</v>
-      </c>
-      <c r="V8" s="235"/>
+      <c r="Q8" s="263" t="s">
+        <v>296</v>
+      </c>
+      <c r="R8" s="264"/>
+      <c r="S8" s="264"/>
+      <c r="T8" s="265"/>
+      <c r="U8" s="268" t="e">
+        <f ca="1">ROUNDUP(SUM(AC28:AC777777)/SUM(AG28:AG777777),2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" s="268"/>
     </row>
     <row r="9" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D9" s="222" t="s">
-        <v>296</v>
-      </c>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
+      <c r="D9" s="255" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
       <c r="H9" s="58" t="s">
-        <v>295</v>
-      </c>
-      <c r="I9" s="61" t="s">
         <v>294</v>
       </c>
-      <c r="J9" s="90"/>
+      <c r="I9" s="225" t="s">
+        <v>212</v>
+      </c>
+      <c r="J9" s="224" t="e">
+        <f ca="1">IF(J5="","","3P,"&amp;J6&amp;"А")</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K9" s="90"/>
       <c r="P9" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="Q9" s="223" t="s">
+      <c r="Q9" s="256" t="s">
         <v>292</v>
       </c>
-      <c r="R9" s="223"/>
-      <c r="S9" s="223"/>
-      <c r="T9" s="223"/>
-      <c r="U9" s="224"/>
-      <c r="V9" s="224"/>
+      <c r="R9" s="256"/>
+      <c r="S9" s="256"/>
+      <c r="T9" s="256"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
     </row>
     <row r="10" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D10" s="222" t="s">
+      <c r="D10" s="255" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="222"/>
-      <c r="F10" s="222"/>
-      <c r="G10" s="222"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
       <c r="I10" s="61" t="s">
         <v>290</v>
       </c>
@@ -14032,20 +14169,20 @@
       <c r="P10" s="61">
         <v>4</v>
       </c>
-      <c r="Q10" s="223"/>
-      <c r="R10" s="223"/>
-      <c r="S10" s="223"/>
-      <c r="T10" s="223"/>
-      <c r="U10" s="224"/>
-      <c r="V10" s="224"/>
+      <c r="Q10" s="256"/>
+      <c r="R10" s="256"/>
+      <c r="S10" s="256"/>
+      <c r="T10" s="256"/>
+      <c r="U10" s="257"/>
+      <c r="V10" s="257"/>
     </row>
     <row r="11" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D11" s="222" t="s">
+      <c r="D11" s="255" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
       <c r="H11" s="97">
         <v>380</v>
       </c>
@@ -14057,24 +14194,24 @@
       <c r="P11" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="Q11" s="249" t="s">
+      <c r="Q11" s="281" t="s">
         <v>286</v>
       </c>
-      <c r="R11" s="250"/>
-      <c r="S11" s="250"/>
-      <c r="T11" s="251"/>
-      <c r="U11" s="252">
+      <c r="R11" s="282"/>
+      <c r="S11" s="282"/>
+      <c r="T11" s="283"/>
+      <c r="U11" s="284">
         <v>1</v>
       </c>
-      <c r="V11" s="253"/>
+      <c r="V11" s="285"/>
     </row>
     <row r="12" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D12" s="222" t="s">
+      <c r="D12" s="255" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
+      <c r="E12" s="255"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="255"/>
       <c r="H12" s="58" t="s">
         <v>284</v>
       </c>
@@ -14086,111 +14223,176 @@
       <c r="P12" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="225" t="s">
+      <c r="Q12" s="258" t="s">
         <v>282</v>
       </c>
-      <c r="R12" s="225"/>
-      <c r="S12" s="225"/>
-      <c r="T12" s="225"/>
-      <c r="U12" s="225">
+      <c r="R12" s="258"/>
+      <c r="S12" s="258"/>
+      <c r="T12" s="258"/>
+      <c r="U12" s="258">
         <v>44.5</v>
       </c>
-      <c r="V12" s="225"/>
+      <c r="V12" s="258"/>
     </row>
     <row r="13" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="255" t="s">
         <v>281</v>
       </c>
-      <c r="E13" s="222"/>
-      <c r="F13" s="222"/>
-      <c r="G13" s="222"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
       <c r="H13" s="58" t="s">
         <v>280</v>
       </c>
       <c r="I13" s="59"/>
       <c r="P13" s="59"/>
-      <c r="Q13" s="225" t="s">
+      <c r="Q13" s="258" t="s">
         <v>279</v>
       </c>
-      <c r="R13" s="225"/>
-      <c r="S13" s="225"/>
-      <c r="T13" s="225"/>
-      <c r="U13" s="225">
+      <c r="R13" s="258"/>
+      <c r="S13" s="258"/>
+      <c r="T13" s="258"/>
+      <c r="U13" s="258">
         <v>44.5</v>
       </c>
-      <c r="V13" s="225"/>
+      <c r="V13" s="258"/>
     </row>
     <row r="14" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D14" s="222" t="s">
+      <c r="D14" s="255" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="222"/>
-      <c r="F14" s="222"/>
-      <c r="G14" s="222"/>
+      <c r="E14" s="255"/>
+      <c r="F14" s="255"/>
+      <c r="G14" s="255"/>
       <c r="H14" s="60" t="str">
         <f>'&lt;zlight&gt;'!G20&amp;"."&amp;'&lt;zlight&gt;'!H20</f>
         <v>.</v>
       </c>
       <c r="I14" s="59"/>
       <c r="P14" s="59"/>
-      <c r="Q14" s="225" t="s">
+      <c r="Q14" s="258" t="s">
         <v>277</v>
       </c>
-      <c r="R14" s="225"/>
-      <c r="S14" s="225"/>
-      <c r="T14" s="225"/>
-      <c r="U14" s="225">
+      <c r="R14" s="258"/>
+      <c r="S14" s="258"/>
+      <c r="T14" s="258"/>
+      <c r="U14" s="258">
         <v>44.5</v>
       </c>
-      <c r="V14" s="225"/>
+      <c r="V14" s="258"/>
     </row>
     <row r="15" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D15" s="222" t="s">
+      <c r="D15" s="255" t="s">
         <v>276</v>
       </c>
-      <c r="E15" s="222"/>
-      <c r="F15" s="222"/>
-      <c r="G15" s="222"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="255"/>
+      <c r="G15" s="255"/>
       <c r="H15" s="58">
         <v>77</v>
       </c>
       <c r="P15" s="59"/>
-      <c r="Q15" s="234" t="s">
+      <c r="Q15" s="267" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="234"/>
-      <c r="S15" s="234"/>
-      <c r="T15" s="234"/>
-      <c r="U15" s="235">
+      <c r="R15" s="267"/>
+      <c r="S15" s="267"/>
+      <c r="T15" s="267"/>
+      <c r="U15" s="268" t="e">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!$C$4:$C$5,MATCH(H11,BD!$B$4:$B$5,0))*U8),2)</f>
-        <v>0</v>
-      </c>
-      <c r="V15" s="235"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" s="268"/>
     </row>
     <row r="16" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="Q16" s="238" t="s">
-        <v>401</v>
-      </c>
-      <c r="R16" s="238"/>
-      <c r="S16" s="238"/>
-      <c r="T16" s="238"/>
-      <c r="U16" s="238" t="e">
+      <c r="Q16" s="271" t="s">
+        <v>398</v>
+      </c>
+      <c r="R16" s="271"/>
+      <c r="S16" s="271"/>
+      <c r="T16" s="271"/>
+      <c r="U16" s="271" t="e">
         <f>INDEX(BB5:BB9,MATCH(1,BD5:BD9,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="V16" s="238"/>
-    </row>
-    <row r="22" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="V16" s="271"/>
+    </row>
+    <row r="22" spans="1:282" x14ac:dyDescent="0.25">
       <c r="L22" s="139" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="23" spans="1:264" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="23" spans="1:282" x14ac:dyDescent="0.25">
       <c r="L23" s="140">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:264" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="HW23" t="str">
+        <f>IF(J5&lt;&gt;"","&lt;zinsertblock&gt;","")</f>
+        <v>&lt;zinsertblock&gt;</v>
+      </c>
+      <c r="HX23" t="e">
+        <f ca="1">IF(J5="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"UGO",BD!$K$4:$CB$4,0))),MATCH(J6,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="HY23" t="e">
+        <f ca="1">IF(J5="","",FU26-$AA$5*8.5+$AA$5*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"MOVEX",BD!$K$4:$CB$4,0))),MATCH(J6,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="HZ23" t="e">
+        <f ca="1">IF(J5="","",FV26+$AA$6*57+$AA$6*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"MOVEY",BD!$K$4:$CB$4,0))),MATCH(J6,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(J5&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="IA23">
+        <f>$AA$5</f>
+        <v>1</v>
+      </c>
+      <c r="IB23">
+        <f>$AA$6</f>
+        <v>1</v>
+      </c>
+      <c r="IC23">
+        <v>0</v>
+      </c>
+      <c r="ID23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="IE23" t="e">
+        <f ca="1">J7&amp;"\P"&amp;J8&amp;"\P"&amp;J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="IF23" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="IG23" t="e">
+        <f ca="1">$J$7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="IH23" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="II23" s="227" t="s">
+        <v>651</v>
+      </c>
+      <c r="IJ23" s="227" t="s">
+        <v>649</v>
+      </c>
+      <c r="IK23">
+        <f>$H$5</f>
+        <v>0</v>
+      </c>
+      <c r="IL23" s="227" t="s">
+        <v>650</v>
+      </c>
+      <c r="IM23" t="e">
+        <f ca="1">J8&amp;","&amp;J9</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="IN23" t="str">
+        <f>IF(J5="","","&lt;/zinsertblock&gt;")</f>
+        <v>&lt;/zinsertblock&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:282" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <f>COLUMN(A24)</f>
         <v>1</v>
@@ -14966,7 +15168,7 @@
         <v>195</v>
       </c>
       <c r="GN24" s="2">
-        <f t="shared" ref="GN24:IQ24" si="3">COLUMN(GN24)</f>
+        <f t="shared" ref="GN24:JI24" si="3">COLUMN(GN24)</f>
         <v>196</v>
       </c>
       <c r="GO24" s="2">
@@ -15061,11 +15263,11 @@
         <f t="shared" si="3"/>
         <v>219</v>
       </c>
-      <c r="HL24" s="2">
+      <c r="HL24" s="222">
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
-      <c r="HM24" s="2">
+      <c r="HM24" s="222">
         <f t="shared" si="3"/>
         <v>221</v>
       </c>
@@ -15141,305 +15343,329 @@
         <f t="shared" si="3"/>
         <v>239</v>
       </c>
-      <c r="IF24" s="2">
-        <f t="shared" si="3"/>
-        <v>240</v>
-      </c>
-      <c r="IG24" s="2">
-        <f t="shared" si="3"/>
-        <v>241</v>
-      </c>
-      <c r="IH24" s="2">
-        <f t="shared" si="3"/>
-        <v>242</v>
-      </c>
-      <c r="II24" s="2">
-        <f t="shared" si="3"/>
-        <v>243</v>
-      </c>
-      <c r="IJ24" s="2">
-        <f t="shared" si="3"/>
-        <v>244</v>
-      </c>
-      <c r="IK24" s="2">
-        <f t="shared" si="3"/>
-        <v>245</v>
-      </c>
-      <c r="IL24" s="2">
-        <f t="shared" si="3"/>
-        <v>246</v>
-      </c>
-      <c r="IM24" s="2">
-        <f t="shared" si="3"/>
-        <v>247</v>
-      </c>
+      <c r="IF24" s="223"/>
+      <c r="IG24" s="223"/>
+      <c r="IH24" s="223"/>
+      <c r="II24" s="223"/>
+      <c r="IJ24" s="223"/>
+      <c r="IK24" s="223"/>
+      <c r="IL24" s="223"/>
+      <c r="IM24" s="223"/>
       <c r="IN24" s="2">
         <f t="shared" si="3"/>
         <v>248</v>
       </c>
-      <c r="IO24" s="2"/>
-      <c r="IP24" s="2"/>
+      <c r="IO24" s="2">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="IP24" s="2">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
       <c r="IQ24" s="2">
         <f t="shared" si="3"/>
         <v>251</v>
       </c>
-      <c r="IR24" s="1">
-        <f t="shared" ref="IR24:JD24" si="4">COLUMN(IR24)</f>
+      <c r="IR24" s="2">
+        <f t="shared" si="3"/>
         <v>252</v>
       </c>
-      <c r="IS24" s="1">
+      <c r="IS24" s="2">
+        <f t="shared" si="3"/>
+        <v>253</v>
+      </c>
+      <c r="IT24" s="2">
+        <f t="shared" si="3"/>
+        <v>254</v>
+      </c>
+      <c r="IU24" s="2">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+      <c r="IV24" s="2">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="IW24" s="2">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+      <c r="IX24" s="223"/>
+      <c r="IY24" s="223"/>
+      <c r="IZ24" s="223"/>
+      <c r="JA24" s="223"/>
+      <c r="JB24" s="223"/>
+      <c r="JC24" s="223"/>
+      <c r="JD24" s="223"/>
+      <c r="JE24" s="223"/>
+      <c r="JF24" s="2">
+        <f t="shared" si="3"/>
+        <v>266</v>
+      </c>
+      <c r="JG24" s="2"/>
+      <c r="JH24" s="2"/>
+      <c r="JI24" s="2">
+        <f t="shared" si="3"/>
+        <v>269</v>
+      </c>
+      <c r="JJ24" s="1">
+        <f t="shared" ref="JJ24:JV24" si="4">COLUMN(JJ24)</f>
+        <v>270</v>
+      </c>
+      <c r="JK24" s="1">
         <f t="shared" si="4"/>
-        <v>253</v>
-      </c>
-      <c r="IT24" s="1">
+        <v>271</v>
+      </c>
+      <c r="JL24" s="1">
         <f t="shared" si="4"/>
-        <v>254</v>
-      </c>
-      <c r="IU24" s="1">
+        <v>272</v>
+      </c>
+      <c r="JM24" s="1">
         <f t="shared" si="4"/>
-        <v>255</v>
-      </c>
-      <c r="IV24" s="1">
+        <v>273</v>
+      </c>
+      <c r="JN24" s="1">
         <f t="shared" si="4"/>
-        <v>256</v>
-      </c>
-      <c r="IW24" s="1">
+        <v>274</v>
+      </c>
+      <c r="JO24" s="1">
         <f t="shared" si="4"/>
-        <v>257</v>
-      </c>
-      <c r="IX24" s="1">
+        <v>275</v>
+      </c>
+      <c r="JP24" s="1">
         <f t="shared" si="4"/>
-        <v>258</v>
-      </c>
-      <c r="IY24" s="1">
+        <v>276</v>
+      </c>
+      <c r="JQ24" s="1">
         <f t="shared" si="4"/>
-        <v>259</v>
-      </c>
-      <c r="IZ24" s="1">
+        <v>277</v>
+      </c>
+      <c r="JR24" s="1">
         <f t="shared" si="4"/>
-        <v>260</v>
-      </c>
-      <c r="JA24" s="1">
+        <v>278</v>
+      </c>
+      <c r="JS24" s="1">
         <f t="shared" si="4"/>
-        <v>261</v>
-      </c>
-      <c r="JB24" s="1">
+        <v>279</v>
+      </c>
+      <c r="JT24" s="1">
         <f t="shared" si="4"/>
-        <v>262</v>
-      </c>
-      <c r="JC24" s="1">
+        <v>280</v>
+      </c>
+      <c r="JU24" s="1">
         <f t="shared" si="4"/>
-        <v>263</v>
-      </c>
-      <c r="JD24" s="1">
+        <v>281</v>
+      </c>
+      <c r="JV24" s="1">
         <f t="shared" si="4"/>
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" spans="1:264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BD25" s="243" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BD25" s="275" t="s">
+        <v>506</v>
+      </c>
+      <c r="BE25" s="276"/>
+      <c r="BF25" s="276"/>
+      <c r="BG25" s="276"/>
+      <c r="BH25" s="276"/>
+      <c r="BI25" s="276"/>
+      <c r="BJ25" s="276"/>
+      <c r="BK25" s="276"/>
+      <c r="BL25" s="276"/>
+      <c r="BM25" s="276"/>
+      <c r="BN25" s="276"/>
+      <c r="BO25" s="276"/>
+      <c r="BP25" s="276"/>
+      <c r="BQ25" s="276"/>
+      <c r="BR25" s="276"/>
+      <c r="BS25" s="276"/>
+      <c r="BT25" s="276"/>
+      <c r="BU25" s="276"/>
+      <c r="BV25" s="276"/>
+      <c r="BW25" s="276"/>
+      <c r="BX25" s="276"/>
+      <c r="BY25" s="276"/>
+      <c r="BZ25" s="276"/>
+      <c r="CA25" s="277"/>
+      <c r="CB25" s="275" t="s">
         <v>509</v>
       </c>
-      <c r="BE25" s="244"/>
-      <c r="BF25" s="244"/>
-      <c r="BG25" s="244"/>
-      <c r="BH25" s="244"/>
-      <c r="BI25" s="244"/>
-      <c r="BJ25" s="244"/>
-      <c r="BK25" s="244"/>
-      <c r="BL25" s="244"/>
-      <c r="BM25" s="244"/>
-      <c r="BN25" s="244"/>
-      <c r="BO25" s="244"/>
-      <c r="BP25" s="244"/>
-      <c r="BQ25" s="244"/>
-      <c r="BR25" s="244"/>
-      <c r="BS25" s="244"/>
-      <c r="BT25" s="244"/>
-      <c r="BU25" s="244"/>
-      <c r="BV25" s="244"/>
-      <c r="BW25" s="244"/>
-      <c r="BX25" s="244"/>
-      <c r="BY25" s="244"/>
-      <c r="BZ25" s="244"/>
-      <c r="CA25" s="245"/>
-      <c r="CB25" s="243" t="s">
-        <v>512</v>
-      </c>
-      <c r="CC25" s="244"/>
-      <c r="CD25" s="244"/>
-      <c r="CE25" s="244"/>
-      <c r="CF25" s="244"/>
-      <c r="CG25" s="244"/>
-      <c r="CH25" s="244"/>
-      <c r="CI25" s="244"/>
-      <c r="CJ25" s="244"/>
-      <c r="CK25" s="244"/>
-      <c r="CL25" s="244"/>
-      <c r="CM25" s="244"/>
-      <c r="CN25" s="244"/>
-      <c r="CO25" s="244"/>
-      <c r="CP25" s="244"/>
-      <c r="CQ25" s="244"/>
-      <c r="CR25" s="244"/>
-      <c r="CS25" s="244"/>
-      <c r="CT25" s="246" t="s">
+      <c r="CC25" s="276"/>
+      <c r="CD25" s="276"/>
+      <c r="CE25" s="276"/>
+      <c r="CF25" s="276"/>
+      <c r="CG25" s="276"/>
+      <c r="CH25" s="276"/>
+      <c r="CI25" s="276"/>
+      <c r="CJ25" s="276"/>
+      <c r="CK25" s="276"/>
+      <c r="CL25" s="276"/>
+      <c r="CM25" s="276"/>
+      <c r="CN25" s="276"/>
+      <c r="CO25" s="276"/>
+      <c r="CP25" s="276"/>
+      <c r="CQ25" s="276"/>
+      <c r="CR25" s="276"/>
+      <c r="CS25" s="276"/>
+      <c r="CT25" s="278" t="s">
         <v>266</v>
       </c>
-      <c r="CU25" s="247"/>
-      <c r="CV25" s="247"/>
-      <c r="CW25" s="247"/>
-      <c r="CX25" s="247"/>
-      <c r="CY25" s="247"/>
-      <c r="CZ25" s="247"/>
-      <c r="DA25" s="247"/>
-      <c r="DB25" s="247"/>
-      <c r="DC25" s="247"/>
-      <c r="DD25" s="247"/>
-      <c r="DE25" s="247"/>
-      <c r="DF25" s="247"/>
-      <c r="DG25" s="247"/>
-      <c r="DH25" s="247"/>
-      <c r="DI25" s="247"/>
-      <c r="DJ25" s="247"/>
-      <c r="DK25" s="247"/>
-      <c r="DL25" s="247"/>
-      <c r="DM25" s="247"/>
-      <c r="DN25" s="247"/>
-      <c r="DO25" s="247"/>
-      <c r="DP25" s="247"/>
-      <c r="DQ25" s="247"/>
-      <c r="DR25" s="247"/>
-      <c r="DS25" s="247"/>
-      <c r="DT25" s="247"/>
-      <c r="DU25" s="247"/>
-      <c r="DV25" s="247"/>
-      <c r="DW25" s="247"/>
-      <c r="DX25" s="247"/>
-      <c r="DY25" s="247"/>
-      <c r="DZ25" s="247"/>
-      <c r="EA25" s="247"/>
-      <c r="EB25" s="247"/>
-      <c r="EC25" s="247"/>
-      <c r="ED25" s="247"/>
-      <c r="EE25" s="247"/>
-      <c r="EF25" s="247"/>
-      <c r="EG25" s="247"/>
-      <c r="EH25" s="247"/>
-      <c r="EI25" s="247"/>
-      <c r="EJ25" s="247"/>
-      <c r="EK25" s="247"/>
-      <c r="EL25" s="247"/>
-      <c r="EM25" s="247"/>
-      <c r="EN25" s="247"/>
-      <c r="EO25" s="247"/>
-      <c r="EP25" s="247"/>
-      <c r="EQ25" s="247"/>
-      <c r="ER25" s="247"/>
-      <c r="ES25" s="247"/>
-      <c r="ET25" s="247"/>
-      <c r="EU25" s="247"/>
-      <c r="EV25" s="247"/>
-      <c r="EW25" s="247"/>
-      <c r="EX25" s="247"/>
-      <c r="EY25" s="247"/>
-      <c r="EZ25" s="247"/>
-      <c r="FA25" s="247"/>
-      <c r="FB25" s="247"/>
-      <c r="FC25" s="247"/>
-      <c r="FD25" s="247"/>
-      <c r="FE25" s="247"/>
-      <c r="FF25" s="247"/>
-      <c r="FG25" s="247"/>
-      <c r="FH25" s="247"/>
-      <c r="FI25" s="247"/>
-      <c r="FJ25" s="247"/>
-      <c r="FK25" s="247"/>
-      <c r="FL25" s="247"/>
-      <c r="FM25" s="247"/>
-      <c r="FN25" s="247"/>
-      <c r="FO25" s="247"/>
-      <c r="FP25" s="248"/>
-    </row>
-    <row r="26" spans="1:264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="236" t="s">
+      <c r="CU25" s="279"/>
+      <c r="CV25" s="279"/>
+      <c r="CW25" s="279"/>
+      <c r="CX25" s="279"/>
+      <c r="CY25" s="279"/>
+      <c r="CZ25" s="279"/>
+      <c r="DA25" s="279"/>
+      <c r="DB25" s="279"/>
+      <c r="DC25" s="279"/>
+      <c r="DD25" s="279"/>
+      <c r="DE25" s="279"/>
+      <c r="DF25" s="279"/>
+      <c r="DG25" s="279"/>
+      <c r="DH25" s="279"/>
+      <c r="DI25" s="279"/>
+      <c r="DJ25" s="279"/>
+      <c r="DK25" s="279"/>
+      <c r="DL25" s="279"/>
+      <c r="DM25" s="279"/>
+      <c r="DN25" s="279"/>
+      <c r="DO25" s="279"/>
+      <c r="DP25" s="279"/>
+      <c r="DQ25" s="279"/>
+      <c r="DR25" s="279"/>
+      <c r="DS25" s="279"/>
+      <c r="DT25" s="279"/>
+      <c r="DU25" s="279"/>
+      <c r="DV25" s="279"/>
+      <c r="DW25" s="279"/>
+      <c r="DX25" s="279"/>
+      <c r="DY25" s="279"/>
+      <c r="DZ25" s="279"/>
+      <c r="EA25" s="279"/>
+      <c r="EB25" s="279"/>
+      <c r="EC25" s="279"/>
+      <c r="ED25" s="279"/>
+      <c r="EE25" s="279"/>
+      <c r="EF25" s="279"/>
+      <c r="EG25" s="279"/>
+      <c r="EH25" s="279"/>
+      <c r="EI25" s="279"/>
+      <c r="EJ25" s="279"/>
+      <c r="EK25" s="279"/>
+      <c r="EL25" s="279"/>
+      <c r="EM25" s="279"/>
+      <c r="EN25" s="279"/>
+      <c r="EO25" s="279"/>
+      <c r="EP25" s="279"/>
+      <c r="EQ25" s="279"/>
+      <c r="ER25" s="279"/>
+      <c r="ES25" s="279"/>
+      <c r="ET25" s="279"/>
+      <c r="EU25" s="279"/>
+      <c r="EV25" s="279"/>
+      <c r="EW25" s="279"/>
+      <c r="EX25" s="279"/>
+      <c r="EY25" s="279"/>
+      <c r="EZ25" s="279"/>
+      <c r="FA25" s="279"/>
+      <c r="FB25" s="279"/>
+      <c r="FC25" s="279"/>
+      <c r="FD25" s="279"/>
+      <c r="FE25" s="279"/>
+      <c r="FF25" s="279"/>
+      <c r="FG25" s="279"/>
+      <c r="FH25" s="279"/>
+      <c r="FI25" s="279"/>
+      <c r="FJ25" s="279"/>
+      <c r="FK25" s="279"/>
+      <c r="FL25" s="279"/>
+      <c r="FM25" s="279"/>
+      <c r="FN25" s="279"/>
+      <c r="FO25" s="279"/>
+      <c r="FP25" s="280"/>
+    </row>
+    <row r="26" spans="1:282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="269" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="233" t="s">
+      <c r="E26" s="266" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="233" t="s">
+      <c r="F26" s="266" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="233" t="s">
+      <c r="G26" s="266" t="s">
         <v>273</v>
       </c>
-      <c r="H26" s="233" t="s">
+      <c r="H26" s="266" t="s">
         <v>272</v>
       </c>
-      <c r="I26" s="233" t="s">
+      <c r="I26" s="266" t="s">
         <v>271</v>
       </c>
-      <c r="J26" s="258" t="s">
-        <v>605</v>
-      </c>
-      <c r="K26" s="237" t="s">
-        <v>385</v>
-      </c>
-      <c r="L26" s="261" t="s">
-        <v>386</v>
-      </c>
-      <c r="M26" s="261"/>
-      <c r="N26" s="261"/>
-      <c r="O26" s="233" t="s">
+      <c r="J26" s="290" t="s">
+        <v>602</v>
+      </c>
+      <c r="K26" s="270" t="s">
+        <v>382</v>
+      </c>
+      <c r="L26" s="293" t="s">
+        <v>383</v>
+      </c>
+      <c r="M26" s="293"/>
+      <c r="N26" s="293"/>
+      <c r="O26" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="P26" s="262" t="s">
+      <c r="P26" s="294" t="s">
         <v>269</v>
       </c>
-      <c r="Q26" s="262"/>
-      <c r="R26" s="262"/>
-      <c r="S26" s="262"/>
-      <c r="T26" s="262"/>
-      <c r="U26" s="262"/>
-      <c r="V26" s="262"/>
-      <c r="W26" s="262"/>
-      <c r="X26" s="262"/>
-      <c r="Y26" s="262"/>
-      <c r="Z26" s="262"/>
-      <c r="AA26" s="262"/>
-      <c r="AB26" s="263" t="s">
+      <c r="Q26" s="294"/>
+      <c r="R26" s="294"/>
+      <c r="S26" s="294"/>
+      <c r="T26" s="294"/>
+      <c r="U26" s="294"/>
+      <c r="V26" s="294"/>
+      <c r="W26" s="294"/>
+      <c r="X26" s="294"/>
+      <c r="Y26" s="294"/>
+      <c r="Z26" s="294"/>
+      <c r="AA26" s="294"/>
+      <c r="AB26" s="295" t="s">
         <v>268</v>
       </c>
-      <c r="AC26" s="263"/>
-      <c r="AD26" s="263"/>
-      <c r="AE26" s="263"/>
-      <c r="AF26" s="263"/>
-      <c r="AG26" s="263"/>
-      <c r="AH26" s="263"/>
-      <c r="AI26" s="263"/>
-      <c r="AJ26" s="263"/>
-      <c r="AK26" s="263"/>
-      <c r="AL26" s="263"/>
-      <c r="AM26" s="263"/>
-      <c r="AN26" s="263" t="s">
+      <c r="AC26" s="295"/>
+      <c r="AD26" s="295"/>
+      <c r="AE26" s="295"/>
+      <c r="AF26" s="295"/>
+      <c r="AG26" s="295"/>
+      <c r="AH26" s="295"/>
+      <c r="AI26" s="295"/>
+      <c r="AJ26" s="295"/>
+      <c r="AK26" s="295"/>
+      <c r="AL26" s="295"/>
+      <c r="AM26" s="295"/>
+      <c r="AN26" s="295" t="s">
         <v>267</v>
       </c>
-      <c r="AO26" s="263"/>
-      <c r="AP26" s="263"/>
-      <c r="AQ26" s="263"/>
-      <c r="AR26" s="263"/>
-      <c r="AS26" s="263"/>
-      <c r="AT26" s="263"/>
-      <c r="AU26" s="263"/>
-      <c r="AV26" s="263"/>
-      <c r="AW26" s="263"/>
-      <c r="AX26" s="263"/>
-      <c r="AY26" s="263"/>
-      <c r="AZ26" s="263"/>
-      <c r="BA26" s="263"/>
-      <c r="BB26" s="263"/>
-      <c r="BC26" s="263"/>
+      <c r="AO26" s="295"/>
+      <c r="AP26" s="295"/>
+      <c r="AQ26" s="295"/>
+      <c r="AR26" s="295"/>
+      <c r="AS26" s="295"/>
+      <c r="AT26" s="295"/>
+      <c r="AU26" s="295"/>
+      <c r="AV26" s="295"/>
+      <c r="AW26" s="295"/>
+      <c r="AX26" s="295"/>
+      <c r="AY26" s="295"/>
+      <c r="AZ26" s="295"/>
+      <c r="BA26" s="295"/>
+      <c r="BB26" s="295"/>
+      <c r="BC26" s="295"/>
       <c r="BD26" s="59"/>
       <c r="BE26" s="59"/>
       <c r="BF26" s="59"/>
@@ -15448,26 +15674,26 @@
       <c r="BI26" s="59"/>
       <c r="BJ26" s="59"/>
       <c r="BK26" s="59"/>
-      <c r="BL26" s="265" t="s">
-        <v>498</v>
-      </c>
-      <c r="BM26" s="265"/>
-      <c r="BN26" s="265"/>
-      <c r="BO26" s="265"/>
-      <c r="BP26" s="265"/>
-      <c r="BQ26" s="265"/>
-      <c r="BR26" s="265"/>
-      <c r="BS26" s="265"/>
+      <c r="BL26" s="297" t="s">
+        <v>495</v>
+      </c>
+      <c r="BM26" s="297"/>
+      <c r="BN26" s="297"/>
+      <c r="BO26" s="297"/>
+      <c r="BP26" s="297"/>
+      <c r="BQ26" s="297"/>
+      <c r="BR26" s="297"/>
+      <c r="BS26" s="297"/>
       <c r="BT26" s="59"/>
       <c r="BU26" s="59"/>
       <c r="BV26" s="59"/>
-      <c r="BW26" s="266" t="s">
-        <v>511</v>
-      </c>
-      <c r="BX26" s="266"/>
-      <c r="BY26" s="266"/>
-      <c r="BZ26" s="266"/>
-      <c r="CA26" s="266"/>
+      <c r="BW26" s="298" t="s">
+        <v>508</v>
+      </c>
+      <c r="BX26" s="298"/>
+      <c r="BY26" s="298"/>
+      <c r="BZ26" s="298"/>
+      <c r="CA26" s="298"/>
       <c r="CB26" s="59"/>
       <c r="CC26" s="59"/>
       <c r="CD26" s="59"/>
@@ -15498,84 +15724,84 @@
       <c r="DC26" s="59"/>
       <c r="DD26" s="59"/>
       <c r="DE26" s="59"/>
-      <c r="DF26" s="255" t="s">
-        <v>530</v>
-      </c>
-      <c r="DG26" s="255"/>
-      <c r="DH26" s="255"/>
-      <c r="DI26" s="255"/>
-      <c r="DJ26" s="255"/>
-      <c r="DK26" s="255"/>
-      <c r="DL26" s="255"/>
-      <c r="DM26" s="255"/>
-      <c r="DN26" s="255"/>
-      <c r="DO26" s="255"/>
-      <c r="DP26" s="255"/>
-      <c r="DQ26" s="255"/>
-      <c r="DR26" s="255"/>
-      <c r="DS26" s="255"/>
-      <c r="DT26" s="255"/>
-      <c r="DU26" s="255"/>
-      <c r="DV26" s="255"/>
-      <c r="DW26" s="255"/>
-      <c r="DX26" s="254" t="s">
+      <c r="DF26" s="287" t="s">
+        <v>527</v>
+      </c>
+      <c r="DG26" s="287"/>
+      <c r="DH26" s="287"/>
+      <c r="DI26" s="287"/>
+      <c r="DJ26" s="287"/>
+      <c r="DK26" s="287"/>
+      <c r="DL26" s="287"/>
+      <c r="DM26" s="287"/>
+      <c r="DN26" s="287"/>
+      <c r="DO26" s="287"/>
+      <c r="DP26" s="287"/>
+      <c r="DQ26" s="287"/>
+      <c r="DR26" s="287"/>
+      <c r="DS26" s="287"/>
+      <c r="DT26" s="287"/>
+      <c r="DU26" s="287"/>
+      <c r="DV26" s="287"/>
+      <c r="DW26" s="287"/>
+      <c r="DX26" s="286" t="s">
         <v>206</v>
       </c>
-      <c r="DY26" s="254"/>
-      <c r="DZ26" s="254"/>
-      <c r="EA26" s="239" t="s">
+      <c r="DY26" s="286"/>
+      <c r="DZ26" s="286"/>
+      <c r="EA26" s="272" t="s">
         <v>205</v>
       </c>
-      <c r="EB26" s="240"/>
-      <c r="EC26" s="240"/>
-      <c r="ED26" s="240"/>
-      <c r="EE26" s="240"/>
-      <c r="EF26" s="240"/>
-      <c r="EG26" s="240"/>
-      <c r="EH26" s="240"/>
-      <c r="EI26" s="240"/>
-      <c r="EJ26" s="240"/>
-      <c r="EK26" s="240"/>
-      <c r="EL26" s="240"/>
-      <c r="EM26" s="240"/>
-      <c r="EN26" s="240"/>
-      <c r="EO26" s="240"/>
-      <c r="EP26" s="240"/>
-      <c r="EQ26" s="256" t="s">
+      <c r="EB26" s="273"/>
+      <c r="EC26" s="273"/>
+      <c r="ED26" s="273"/>
+      <c r="EE26" s="273"/>
+      <c r="EF26" s="273"/>
+      <c r="EG26" s="273"/>
+      <c r="EH26" s="273"/>
+      <c r="EI26" s="273"/>
+      <c r="EJ26" s="273"/>
+      <c r="EK26" s="273"/>
+      <c r="EL26" s="273"/>
+      <c r="EM26" s="273"/>
+      <c r="EN26" s="273"/>
+      <c r="EO26" s="273"/>
+      <c r="EP26" s="273"/>
+      <c r="EQ26" s="288" t="s">
         <v>204</v>
       </c>
-      <c r="ER26" s="256"/>
-      <c r="ES26" s="256"/>
-      <c r="ET26" s="256"/>
-      <c r="EU26" s="256"/>
-      <c r="EV26" s="256"/>
-      <c r="EW26" s="257" t="s">
+      <c r="ER26" s="288"/>
+      <c r="ES26" s="288"/>
+      <c r="ET26" s="288"/>
+      <c r="EU26" s="288"/>
+      <c r="EV26" s="288"/>
+      <c r="EW26" s="289" t="s">
         <v>203</v>
       </c>
-      <c r="EX26" s="257"/>
-      <c r="EY26" s="257"/>
-      <c r="EZ26" s="257"/>
-      <c r="FA26" s="257" t="s">
+      <c r="EX26" s="289"/>
+      <c r="EY26" s="289"/>
+      <c r="EZ26" s="289"/>
+      <c r="FA26" s="289" t="s">
         <v>202</v>
       </c>
-      <c r="FB26" s="257"/>
-      <c r="FC26" s="257"/>
-      <c r="FD26" s="257"/>
-      <c r="FE26" s="257" t="s">
+      <c r="FB26" s="289"/>
+      <c r="FC26" s="289"/>
+      <c r="FD26" s="289"/>
+      <c r="FE26" s="289" t="s">
         <v>201</v>
       </c>
-      <c r="FF26" s="257"/>
-      <c r="FG26" s="257"/>
-      <c r="FH26" s="257"/>
-      <c r="FI26" s="257"/>
-      <c r="FJ26" s="257"/>
-      <c r="FK26" s="257" t="s">
+      <c r="FF26" s="289"/>
+      <c r="FG26" s="289"/>
+      <c r="FH26" s="289"/>
+      <c r="FI26" s="289"/>
+      <c r="FJ26" s="289"/>
+      <c r="FK26" s="289" t="s">
         <v>200</v>
       </c>
-      <c r="FL26" s="257"/>
-      <c r="FM26" s="257"/>
-      <c r="FN26" s="257"/>
-      <c r="FO26" s="257"/>
+      <c r="FL26" s="289"/>
+      <c r="FM26" s="289"/>
+      <c r="FN26" s="289"/>
+      <c r="FO26" s="289"/>
       <c r="FP26" s="59"/>
       <c r="FQ26" s="81"/>
       <c r="FR26" s="81"/>
@@ -15642,30 +15868,37 @@
       <c r="GJ26" t="s">
         <v>259</v>
       </c>
-      <c r="GK26" t="str">
-        <f>"Коэффициент мощности, cosf = "&amp;U8</f>
-        <v>Коэффициент мощности, cosf = 0,92</v>
+      <c r="GK26" t="e">
+        <f ca="1">"Коэффициент мощности, cosf = "&amp;U8</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="GL26" t="s">
         <v>258</v>
       </c>
-      <c r="GM26" t="str">
+      <c r="GM26" t="e">
         <f ca="1">"Расчетный ток, Iр = "&amp;U15&amp;"А"</f>
-        <v>Расчетный ток, Iр = 0А</v>
-      </c>
-      <c r="HL26" t="s">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GN26" t="s">
+        <v>515</v>
+      </c>
+      <c r="GO26" t="str">
+        <f>IF(J5="АВ","INTEGER_1","INTEGER_2")</f>
+        <v>INTEGER_1</v>
+      </c>
+      <c r="HN26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:264" ht="103.5" x14ac:dyDescent="0.25">
-      <c r="D27" s="236"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="233"/>
-      <c r="H27" s="233"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="259"/>
-      <c r="K27" s="237"/>
+    <row r="27" spans="1:282" ht="103.5" x14ac:dyDescent="0.25">
+      <c r="D27" s="269"/>
+      <c r="E27" s="266"/>
+      <c r="F27" s="266"/>
+      <c r="G27" s="266"/>
+      <c r="H27" s="266"/>
+      <c r="I27" s="266"/>
+      <c r="J27" s="291"/>
+      <c r="K27" s="270"/>
       <c r="L27" s="91" t="s">
         <v>257</v>
       </c>
@@ -15675,9 +15908,9 @@
       <c r="N27" s="91" t="s">
         <v>255</v>
       </c>
-      <c r="O27" s="233"/>
+      <c r="O27" s="266"/>
       <c r="P27" s="161" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Q27" s="161" t="s">
         <v>254</v>
@@ -15716,13 +15949,13 @@
         <v>244</v>
       </c>
       <c r="AC27" s="166" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AD27" s="166" t="s">
         <v>242</v>
       </c>
       <c r="AE27" s="166" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AF27" s="166" t="s">
         <v>241</v>
@@ -15734,13 +15967,13 @@
         <v>243</v>
       </c>
       <c r="AI27" s="166" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AJ27" s="166" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AK27" s="166" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AL27" s="166" t="s">
         <v>221</v>
@@ -15776,13 +16009,13 @@
         <v>231</v>
       </c>
       <c r="AW27" s="167" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AX27" s="166" t="s">
         <v>230</v>
       </c>
       <c r="AY27" s="212" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="AZ27" s="166" t="s">
         <v>229</v>
@@ -15797,28 +16030,28 @@
         <v>226</v>
       </c>
       <c r="BD27" s="168" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="BE27" s="168" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="BF27" s="168" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="BG27" s="169" t="s">
         <v>222</v>
       </c>
       <c r="BH27" s="170" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="BI27" s="171" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="BJ27" s="172" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="BK27" s="173" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="BL27" s="166" t="s">
         <v>223</v>
@@ -15836,22 +16069,22 @@
         <v>218</v>
       </c>
       <c r="BQ27" s="174" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="BR27" s="166" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="BS27" s="166" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="BT27" s="172" t="s">
         <v>217</v>
       </c>
       <c r="BU27" s="172" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="BV27" s="171" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="BW27" s="173" t="s">
         <v>216</v>
@@ -15869,13 +16102,13 @@
         <v>212</v>
       </c>
       <c r="CB27" s="168" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="CC27" s="169" t="s">
         <v>222</v>
       </c>
       <c r="CD27" s="169" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="CE27" s="172" t="s">
         <v>221</v>
@@ -15884,28 +16117,28 @@
         <v>220</v>
       </c>
       <c r="CG27" s="166" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="CH27" s="174" t="s">
         <v>218</v>
       </c>
       <c r="CI27" s="174" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="CJ27" s="166" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="CK27" s="166" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="CL27" s="172" t="s">
         <v>217</v>
       </c>
       <c r="CM27" s="172" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="CN27" s="171" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="CO27" s="173" t="s">
         <v>216</v>
@@ -15923,228 +16156,228 @@
         <v>212</v>
       </c>
       <c r="CT27" s="81" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="CU27" s="81" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="CV27" s="81" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="CW27" s="175" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="CX27" s="176" t="s">
+        <v>406</v>
+      </c>
+      <c r="CY27" s="176" t="s">
+        <v>407</v>
+      </c>
+      <c r="CZ27" s="176" t="s">
+        <v>408</v>
+      </c>
+      <c r="DA27" s="176" t="s">
+        <v>465</v>
+      </c>
+      <c r="DB27" s="176" t="s">
         <v>409</v>
       </c>
-      <c r="CY27" s="176" t="s">
+      <c r="DC27" s="177" t="s">
         <v>410</v>
       </c>
-      <c r="CZ27" s="176" t="s">
-        <v>411</v>
-      </c>
-      <c r="DA27" s="176" t="s">
-        <v>468</v>
-      </c>
-      <c r="DB27" s="176" t="s">
-        <v>412</v>
-      </c>
-      <c r="DC27" s="177" t="s">
-        <v>413</v>
-      </c>
       <c r="DD27" s="177" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="DE27" s="82"/>
       <c r="DF27" s="178" t="s">
+        <v>523</v>
+      </c>
+      <c r="DG27" s="178" t="s">
+        <v>524</v>
+      </c>
+      <c r="DH27" s="179" t="s">
+        <v>547</v>
+      </c>
+      <c r="DI27" s="179" t="s">
+        <v>548</v>
+      </c>
+      <c r="DJ27" s="179" t="s">
+        <v>549</v>
+      </c>
+      <c r="DK27" s="180" t="s">
+        <v>535</v>
+      </c>
+      <c r="DL27" s="180" t="s">
+        <v>525</v>
+      </c>
+      <c r="DM27" s="180" t="s">
+        <v>575</v>
+      </c>
+      <c r="DN27" s="180" t="s">
+        <v>576</v>
+      </c>
+      <c r="DO27" s="154" t="s">
+        <v>512</v>
+      </c>
+      <c r="DP27" s="154" t="s">
+        <v>513</v>
+      </c>
+      <c r="DQ27" s="154" t="s">
+        <v>514</v>
+      </c>
+      <c r="DR27" s="178" t="s">
         <v>526</v>
       </c>
-      <c r="DG27" s="178" t="s">
-        <v>527</v>
-      </c>
-      <c r="DH27" s="179" t="s">
+      <c r="DS27" s="180" t="s">
+        <v>528</v>
+      </c>
+      <c r="DT27" s="181" t="s">
+        <v>529</v>
+      </c>
+      <c r="DU27" s="181" t="s">
+        <v>513</v>
+      </c>
+      <c r="DV27" s="181" t="s">
+        <v>514</v>
+      </c>
+      <c r="DW27" s="180" t="s">
+        <v>530</v>
+      </c>
+      <c r="DX27" s="157" t="s">
+        <v>532</v>
+      </c>
+      <c r="DY27" s="157" t="s">
+        <v>533</v>
+      </c>
+      <c r="DZ27" s="158" t="s">
+        <v>508</v>
+      </c>
+      <c r="EA27" s="182" t="s">
+        <v>534</v>
+      </c>
+      <c r="EB27" s="182" t="s">
+        <v>536</v>
+      </c>
+      <c r="EC27" s="182" t="s">
+        <v>537</v>
+      </c>
+      <c r="ED27" s="183" t="s">
+        <v>539</v>
+      </c>
+      <c r="EE27" s="184" t="s">
+        <v>540</v>
+      </c>
+      <c r="EF27" s="184" t="s">
+        <v>541</v>
+      </c>
+      <c r="EG27" s="184" t="s">
+        <v>514</v>
+      </c>
+      <c r="EH27" s="184" t="s">
+        <v>542</v>
+      </c>
+      <c r="EI27" s="184" t="s">
+        <v>543</v>
+      </c>
+      <c r="EJ27" s="184" t="s">
+        <v>582</v>
+      </c>
+      <c r="EK27" s="184" t="s">
+        <v>583</v>
+      </c>
+      <c r="EL27" s="185" t="s">
+        <v>580</v>
+      </c>
+      <c r="EM27" s="186" t="s">
+        <v>544</v>
+      </c>
+      <c r="EN27" s="187" t="s">
+        <v>538</v>
+      </c>
+      <c r="EO27" s="188" t="s">
         <v>550</v>
       </c>
-      <c r="DI27" s="179" t="s">
+      <c r="EP27" s="189" t="s">
+        <v>508</v>
+      </c>
+      <c r="EQ27" s="186" t="s">
+        <v>545</v>
+      </c>
+      <c r="ER27" s="186" t="s">
+        <v>546</v>
+      </c>
+      <c r="ES27" s="190" t="s">
+        <v>552</v>
+      </c>
+      <c r="ET27" s="190" t="s">
+        <v>553</v>
+      </c>
+      <c r="EU27" s="190" t="s">
         <v>551</v>
       </c>
-      <c r="DJ27" s="179" t="s">
-        <v>552</v>
-      </c>
-      <c r="DK27" s="180" t="s">
-        <v>538</v>
-      </c>
-      <c r="DL27" s="180" t="s">
-        <v>528</v>
-      </c>
-      <c r="DM27" s="180" t="s">
-        <v>578</v>
-      </c>
-      <c r="DN27" s="180" t="s">
-        <v>579</v>
-      </c>
-      <c r="DO27" s="154" t="s">
-        <v>515</v>
-      </c>
-      <c r="DP27" s="154" t="s">
-        <v>516</v>
-      </c>
-      <c r="DQ27" s="154" t="s">
-        <v>517</v>
-      </c>
-      <c r="DR27" s="178" t="s">
-        <v>529</v>
-      </c>
-      <c r="DS27" s="180" t="s">
-        <v>531</v>
-      </c>
-      <c r="DT27" s="181" t="s">
-        <v>532</v>
-      </c>
-      <c r="DU27" s="181" t="s">
-        <v>516</v>
-      </c>
-      <c r="DV27" s="181" t="s">
-        <v>517</v>
-      </c>
-      <c r="DW27" s="180" t="s">
-        <v>533</v>
-      </c>
-      <c r="DX27" s="157" t="s">
-        <v>535</v>
-      </c>
-      <c r="DY27" s="157" t="s">
-        <v>536</v>
-      </c>
-      <c r="DZ27" s="158" t="s">
-        <v>511</v>
-      </c>
-      <c r="EA27" s="182" t="s">
-        <v>537</v>
-      </c>
-      <c r="EB27" s="182" t="s">
-        <v>539</v>
-      </c>
-      <c r="EC27" s="182" t="s">
-        <v>540</v>
-      </c>
-      <c r="ED27" s="183" t="s">
-        <v>542</v>
-      </c>
-      <c r="EE27" s="184" t="s">
-        <v>543</v>
-      </c>
-      <c r="EF27" s="184" t="s">
-        <v>544</v>
-      </c>
-      <c r="EG27" s="184" t="s">
-        <v>517</v>
-      </c>
-      <c r="EH27" s="184" t="s">
-        <v>545</v>
-      </c>
-      <c r="EI27" s="184" t="s">
-        <v>546</v>
-      </c>
-      <c r="EJ27" s="184" t="s">
-        <v>585</v>
-      </c>
-      <c r="EK27" s="184" t="s">
-        <v>586</v>
-      </c>
-      <c r="EL27" s="185" t="s">
-        <v>583</v>
-      </c>
-      <c r="EM27" s="186" t="s">
-        <v>547</v>
-      </c>
-      <c r="EN27" s="187" t="s">
-        <v>541</v>
-      </c>
-      <c r="EO27" s="188" t="s">
-        <v>553</v>
-      </c>
-      <c r="EP27" s="189" t="s">
-        <v>511</v>
-      </c>
-      <c r="EQ27" s="186" t="s">
-        <v>548</v>
-      </c>
-      <c r="ER27" s="186" t="s">
-        <v>549</v>
-      </c>
-      <c r="ES27" s="190" t="s">
+      <c r="EV27" s="191" t="s">
+        <v>508</v>
+      </c>
+      <c r="EW27" s="190" t="s">
+        <v>554</v>
+      </c>
+      <c r="EX27" s="190" t="s">
         <v>555</v>
       </c>
-      <c r="ET27" s="190" t="s">
+      <c r="EY27" s="190" t="s">
         <v>556</v>
       </c>
-      <c r="EU27" s="190" t="s">
-        <v>554</v>
-      </c>
-      <c r="EV27" s="191" t="s">
-        <v>511</v>
-      </c>
-      <c r="EW27" s="190" t="s">
-        <v>557</v>
-      </c>
-      <c r="EX27" s="190" t="s">
-        <v>558</v>
-      </c>
-      <c r="EY27" s="190" t="s">
-        <v>559</v>
-      </c>
       <c r="EZ27" s="191" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="FA27" s="191" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="FB27" s="191"/>
       <c r="FC27" s="191"/>
       <c r="FD27" s="191" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="FE27" s="191" t="s">
+        <v>574</v>
+      </c>
+      <c r="FF27" s="192" t="s">
         <v>577</v>
       </c>
-      <c r="FF27" s="192" t="s">
-        <v>580</v>
-      </c>
       <c r="FG27" s="192" t="s">
+        <v>578</v>
+      </c>
+      <c r="FH27" s="192" t="s">
+        <v>579</v>
+      </c>
+      <c r="FI27" s="192" t="s">
         <v>581</v>
       </c>
-      <c r="FH27" s="192" t="s">
-        <v>582</v>
-      </c>
-      <c r="FI27" s="192" t="s">
-        <v>584</v>
-      </c>
       <c r="FJ27" s="192" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="FK27" s="191" t="s">
+        <v>570</v>
+      </c>
+      <c r="FL27" s="191" t="s">
+        <v>571</v>
+      </c>
+      <c r="FM27" s="191" t="s">
+        <v>572</v>
+      </c>
+      <c r="FN27" s="191" t="s">
         <v>573</v>
       </c>
-      <c r="FL27" s="191" t="s">
-        <v>574</v>
-      </c>
-      <c r="FM27" s="191" t="s">
-        <v>575</v>
-      </c>
-      <c r="FN27" s="191" t="s">
-        <v>576</v>
-      </c>
       <c r="FO27" s="191" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="FP27" s="193" t="s">
-        <v>427</v>
-      </c>
-      <c r="FQ27" s="267" t="s">
-        <v>588</v>
-      </c>
-      <c r="FR27" s="267"/>
+        <v>424</v>
+      </c>
+      <c r="FQ27" s="299" t="s">
+        <v>585</v>
+      </c>
+      <c r="FR27" s="299"/>
       <c r="FU27" s="113">
         <f>35*$AA$5</f>
         <v>35</v>
@@ -16170,48 +16403,64 @@
       <c r="GQ27" s="104"/>
       <c r="GR27" s="104"/>
       <c r="GS27" s="104"/>
-      <c r="HM27" s="264" t="s">
-        <v>416</v>
-      </c>
-      <c r="HN27" s="264"/>
-      <c r="HO27" s="264"/>
-      <c r="HP27" s="264"/>
-      <c r="HQ27" s="264"/>
-      <c r="HR27" s="264"/>
-      <c r="HS27" s="264"/>
-      <c r="HT27" s="264"/>
-      <c r="HU27" s="242" t="s">
+      <c r="HO27" s="296" t="s">
+        <v>413</v>
+      </c>
+      <c r="HP27" s="296"/>
+      <c r="HQ27" s="296"/>
+      <c r="HR27" s="296"/>
+      <c r="HS27" s="296"/>
+      <c r="HT27" s="296"/>
+      <c r="HU27" s="296"/>
+      <c r="HV27" s="296"/>
+      <c r="HW27" s="274" t="s">
         <v>211</v>
       </c>
-      <c r="HV27" s="242"/>
-      <c r="HW27" s="242"/>
-      <c r="HX27" s="242"/>
-      <c r="HY27" s="242"/>
-      <c r="HZ27" s="242"/>
-      <c r="IA27" s="242"/>
-      <c r="IB27" s="242"/>
-      <c r="IC27" s="242"/>
-      <c r="ID27" s="242"/>
-      <c r="IE27" s="260" t="s">
+      <c r="HX27" s="274"/>
+      <c r="HY27" s="274"/>
+      <c r="HZ27" s="274"/>
+      <c r="IA27" s="274"/>
+      <c r="IB27" s="274"/>
+      <c r="IC27" s="274"/>
+      <c r="ID27" s="274"/>
+      <c r="IE27" s="274"/>
+      <c r="IF27" s="274"/>
+      <c r="IG27" s="274"/>
+      <c r="IH27" s="274"/>
+      <c r="II27" s="274"/>
+      <c r="IJ27" s="274"/>
+      <c r="IK27" s="274"/>
+      <c r="IL27" s="274"/>
+      <c r="IM27" s="274"/>
+      <c r="IN27" s="274"/>
+      <c r="IO27" s="292" t="s">
         <v>210</v>
       </c>
-      <c r="IF27" s="260"/>
-      <c r="IG27" s="260"/>
-      <c r="IH27" s="260"/>
-      <c r="II27" s="260"/>
-      <c r="IJ27" s="260"/>
-      <c r="IK27" s="260"/>
-      <c r="IL27" s="260"/>
-      <c r="IM27" s="260"/>
-      <c r="IN27" s="260"/>
-      <c r="IO27" s="214" t="s">
+      <c r="IP27" s="292"/>
+      <c r="IQ27" s="292"/>
+      <c r="IR27" s="292"/>
+      <c r="IS27" s="292"/>
+      <c r="IT27" s="292"/>
+      <c r="IU27" s="292"/>
+      <c r="IV27" s="292"/>
+      <c r="IW27" s="292"/>
+      <c r="IX27" s="292"/>
+      <c r="IY27" s="292"/>
+      <c r="IZ27" s="292"/>
+      <c r="JA27" s="292"/>
+      <c r="JB27" s="292"/>
+      <c r="JC27" s="292"/>
+      <c r="JD27" s="292"/>
+      <c r="JE27" s="292"/>
+      <c r="JF27" s="292"/>
+      <c r="JG27" s="214" t="s">
         <v>237</v>
       </c>
-      <c r="IP27" s="214"/>
-    </row>
-    <row r="28" spans="1:264" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="JH27" s="214"/>
+    </row>
+    <row r="28" spans="1:282" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C28" s="208" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D28" s="57">
         <f>IF(COUNT($CU$28:CU28)=MATCH(CT28,$CT$28:CT28,0),CT28,"")</f>
@@ -16301,7 +16550,7 @@
         <v>1</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AA28" s="49">
         <f>'&lt;zalldev&gt;EXPORT'!P11</f>
@@ -16895,7 +17144,7 @@
         <v>207</v>
       </c>
       <c r="GA28" s="1" t="e">
-        <f ca="1">IF(R28="ABC","BOOLEAN_1","BOOLEAN_0")</f>
+        <f ca="1">IF(R28="АВС","BOOLEAN_1","BOOLEAN_0")</f>
         <v>#N/A</v>
       </c>
       <c r="GB28" s="156" t="s">
@@ -16906,14 +17155,14 @@
         <v>#N/A</v>
       </c>
       <c r="GD28" s="101" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="GE28" s="151" t="e">
         <f ca="1">IF(H28="",IF(GC28&lt;&gt;"INTEGER_0","INTEGER_2","INTEGER_0"),IF(BU28&lt;&gt;"N","INTEGER_1","INTEGER_2"))</f>
         <v>#N/A</v>
       </c>
       <c r="GF28" s="101" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="GG28" s="150" t="e">
         <f ca="1">IF(GC28="INTEGER_2","INTEGER_2",IF(GC28="INTEGER_3","INTEGER_2",IF(CM28="N","INTEGER_2",IF(CM28=0,"INTEGER_1","INTEGER_0"))))</f>
@@ -16979,14 +17228,14 @@
         <v>197</v>
       </c>
       <c r="GY28" s="113" t="e">
-        <f ca="1">IF(DB28&gt;0,"",U28)</f>
+        <f ca="1">IF(DB28&gt;0,"",U28&amp;"A; (cosf="&amp;T28&amp;")")</f>
         <v>#N/A</v>
       </c>
       <c r="GZ28" s="1" t="s">
         <v>196</v>
       </c>
       <c r="HA28" s="129" t="e">
-        <f ca="1">IF(DB28&gt;0,"",AA28&amp;"\P~"&amp;Q28&amp;"V"&amp;"\P пом. "&amp;IP28)</f>
+        <f ca="1">IF(DB28&gt;0,"",AA28&amp;"\P~"&amp;Q28&amp;"V"&amp;" пом. "&amp;JH28)</f>
         <v>#N/A</v>
       </c>
       <c r="HB28" s="52" t="s">
@@ -17022,140 +17271,202 @@
         <v>VSCHEMACable22</v>
       </c>
       <c r="HK28" s="113" t="e">
-        <f>IF(HG28="",IO28,"")</f>
+        <f>IF(HG28="",JG28,"")</f>
         <v>#N/A</v>
       </c>
-      <c r="HL28" s="1" t="s">
+      <c r="HL28" s="52" t="str">
+        <f>"VSCHEMAAddtext"</f>
+        <v>VSCHEMAAddtext</v>
+      </c>
+      <c r="HM28" s="113" t="e">
+        <f ca="1">IF(AH28="","","dU="&amp;AH28&amp;"%")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="HN28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="HM28" s="106" t="s">
+      <c r="HO28" s="106" t="s">
         <v>209</v>
       </c>
-      <c r="HN28" s="113" t="str">
+      <c r="HP28" s="113" t="str">
         <f>'&lt;zalldev&gt;EXPORT'!AP11</f>
         <v>&lt;zcadnameblock&gt;</v>
       </c>
-      <c r="HO28" s="113" t="e">
-        <f>FU28+12.5*$AA$5+INDEX(BDUGO!$D$4:$D$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))*$AA$5</f>
+      <c r="HQ28" s="113" t="e">
+        <f>FU28+12.5*$AA$5+INDEX(BDUGO!$D$4:$D$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0))*$AA$5</f>
         <v>#N/A</v>
       </c>
-      <c r="HP28" s="113" t="e">
-        <f>FV28+42.5*$AA$6+INDEX(BDUGO!$E$4:$E$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))*$AA$6</f>
+      <c r="HR28" s="113" t="e">
+        <f>FV28+42.5*$AA$6+INDEX(BDUGO!$E$4:$E$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0))*$AA$6</f>
         <v>#N/A</v>
       </c>
-      <c r="HQ28" s="113" t="e">
-        <f>IF(INDEX(BDUGO!$F$4:$F$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))=0,1,INDEX(BDUGO!$F$4:$F$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0)))*$AA$5</f>
+      <c r="HS28" s="113" t="e">
+        <f>IF(INDEX(BDUGO!$F$4:$F$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0))=0,1,INDEX(BDUGO!$F$4:$F$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0)))*$AA$5</f>
         <v>#N/A</v>
       </c>
-      <c r="HR28" s="113" t="e">
-        <f>IF(INDEX(BDUGO!$G$4:$G$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))=0,1,INDEX(BDUGO!$G$4:$G$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0)))*$AA$6</f>
+      <c r="HT28" s="113" t="e">
+        <f>IF(INDEX(BDUGO!$G$4:$G$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0))=0,1,INDEX(BDUGO!$G$4:$G$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0)))*$AA$6</f>
         <v>#N/A</v>
       </c>
-      <c r="HS28" s="113" t="e">
-        <f>INDEX(BDUGO!$H$4:$H$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))</f>
+      <c r="HU28" s="113" t="e">
+        <f>INDEX(BDUGO!$H$4:$H$59,MATCH(IF(DB28&gt;0,"UU","")&amp;HP28,BDUGO!$C$4:$C$59,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="HT28" s="106" t="s">
+      <c r="HV28" s="106" t="s">
         <v>191</v>
       </c>
-      <c r="HU28" s="1" t="e">
+      <c r="HW28" s="1" t="e">
         <f ca="1">IF(H28&lt;&gt;"","&lt;zinsertblock&gt;","")</f>
         <v>#N/A</v>
       </c>
-      <c r="HV28" s="1" t="e">
-        <f ca="1">IF(HU28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"UGO",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+      <c r="HX28" s="1" t="e">
+        <f ca="1">IF(HW28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"UGO",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="HW28" s="1" t="e">
-        <f ca="1">IF(HU28="","",FU28+$AA$5*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"MOVEX",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+      <c r="HY28" s="1" t="e">
+        <f ca="1">IF(HW28="","",FU28+$AA$5*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"MOVEX",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="HX28" s="1" t="e">
-        <f ca="1">IF(HU28="","",FV28+$AA$6*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"MOVEY",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
+      <c r="HZ28" s="1" t="e">
+        <f ca="1">IF(HW28="","",FV28+$AA$6*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"MOVEY",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="HY28" s="1">
+      <c r="IA28" s="1">
         <f>$AA$5</f>
         <v>1</v>
       </c>
-      <c r="HZ28" s="1">
+      <c r="IB28" s="1">
         <f>$AA$6</f>
         <v>1</v>
       </c>
-      <c r="IA28" s="1">
-        <v>0</v>
-      </c>
-      <c r="IB28" s="1" t="s">
+      <c r="IC28" s="1">
+        <v>0</v>
+      </c>
+      <c r="ID28" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="IC28" s="1" t="e">
+      <c r="IE28" s="1" t="e">
         <f ca="1">BY28&amp;"\P"&amp;BZ28&amp;"\P"&amp;CA28</f>
         <v>#N/A</v>
       </c>
-      <c r="ID28" s="1" t="e">
-        <f ca="1">IF(HU28="","","&lt;/zinsertblock&gt;")</f>
+      <c r="IF28" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="IG28" s="1" t="e">
+        <f ca="1">BY28</f>
         <v>#N/A</v>
       </c>
-      <c r="IE28" s="1" t="e">
+      <c r="IH28" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="II28" s="227" t="s">
+        <v>651</v>
+      </c>
+      <c r="IJ28" s="227" t="s">
+        <v>649</v>
+      </c>
+      <c r="IK28" s="1">
+        <f>$H$5</f>
+        <v>0</v>
+      </c>
+      <c r="IL28" s="227" t="s">
+        <v>650</v>
+      </c>
+      <c r="IM28" s="1" t="e">
+        <f ca="1">BZ28&amp;","&amp;CA28</f>
+        <v>#N/A</v>
+      </c>
+      <c r="IN28" s="1" t="e">
+        <f ca="1">IF(HW28="","","&lt;/zinsertblock&gt;")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="IO28" s="1" t="e">
         <f ca="1">IF(I28&lt;&gt;"","&lt;zinsertblock&gt;","")</f>
         <v>#N/A</v>
       </c>
-      <c r="IF28" s="1" t="e">
-        <f ca="1">IF(IE28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"UGO",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
+      <c r="IP28" s="1" t="e">
+        <f ca="1">IF(IO28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"UGO",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="IG28" s="1" t="e">
-        <f ca="1">IF(IE28="","",FU28+$AA$5*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"MOVEX",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
+      <c r="IQ28" s="1" t="e">
+        <f ca="1">IF(IO28="","",FU28+$AA$5*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"MOVEX",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="IH28" s="1" t="e">
-        <f ca="1">IF(IE28="","",FV28-20*$AA$6+$AA$6*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"MOVEY",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
+      <c r="IR28" s="1" t="e">
+        <f ca="1">IF(IO28="","",FV28-20*$AA$6+$AA$6*INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"MOVEY",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="II28" s="1">
+      <c r="IS28" s="1">
         <f>$AA$5</f>
         <v>1</v>
       </c>
-      <c r="IJ28" s="1">
+      <c r="IT28" s="1">
         <f>$AA$6</f>
         <v>1</v>
       </c>
-      <c r="IK28" s="1">
-        <v>0</v>
-      </c>
-      <c r="IL28" s="1" t="s">
+      <c r="IU28" s="1">
+        <v>0</v>
+      </c>
+      <c r="IV28" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="IM28" s="1" t="e">
+      <c r="IW28" s="1" t="e">
         <f ca="1">CQ28&amp;"\P"&amp;CR28&amp;"\P"&amp;CS28</f>
         <v>#N/A</v>
       </c>
-      <c r="IN28" s="1" t="e">
-        <f ca="1">IF(IE28="","","&lt;/zinsertblock&gt;")</f>
+      <c r="IX28" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="IY28" s="1" t="e">
+        <f ca="1">CQ28</f>
         <v>#N/A</v>
       </c>
-      <c r="IO28" s="1" t="e">
+      <c r="IZ28" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="JA28" s="227" t="s">
+        <v>651</v>
+      </c>
+      <c r="JB28" s="227" t="s">
+        <v>649</v>
+      </c>
+      <c r="JC28" s="1">
+        <f>$H$5</f>
+        <v>0</v>
+      </c>
+      <c r="JD28" s="227" t="s">
+        <v>650</v>
+      </c>
+      <c r="JE28" s="1" t="e">
+        <f ca="1">CR28&amp;","&amp;CS28</f>
+        <v>#N/A</v>
+      </c>
+      <c r="JF28" s="1" t="e">
+        <f ca="1">IF(IO28="","","&lt;/zinsertblock&gt;")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="JG28" s="1" t="e">
         <f>IF(AN28="","",INDEX('&lt;zallcab&gt;CabGroup'!$Q$7:$Q$700000,MATCH(AN28,'&lt;zallcab&gt;CabGroup'!$C$7:$C$700000,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="IP28" s="1" t="str">
+      <c r="JH28" s="1" t="str">
         <f ca="1">IF(GU28="","",INDEX('&lt;zalldev&gt;DevGroup'!$R$7:$R$700000,MATCH(DA28&amp;"."&amp;P28,'&lt;zalldev&gt;DevGroup'!$G$7:$G$700000,0)))</f>
         <v>0</v>
       </c>
-      <c r="IQ28" s="1" t="s">
+      <c r="JI28" s="1" t="s">
         <v>189</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="66">
     <mergeCell ref="J26:J27"/>
-    <mergeCell ref="IE27:IN27"/>
+    <mergeCell ref="IO27:JF27"/>
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="O26:O27"/>
     <mergeCell ref="P26:AA26"/>
     <mergeCell ref="AB26:AM26"/>
     <mergeCell ref="AN26:BC26"/>
-    <mergeCell ref="HM27:HT27"/>
+    <mergeCell ref="HO27:HV27"/>
     <mergeCell ref="BL26:BS26"/>
     <mergeCell ref="BW26:CA26"/>
     <mergeCell ref="EW26:EZ26"/>
@@ -17165,7 +17476,7 @@
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="EA26:EP26"/>
     <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="HU27:ID27"/>
+    <mergeCell ref="HW27:IN27"/>
     <mergeCell ref="BD25:CA25"/>
     <mergeCell ref="CT25:FP25"/>
     <mergeCell ref="CB25:CS25"/>
@@ -17217,118 +17528,118 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="Q28:T28">
-    <cfRule type="expression" dxfId="32" priority="100">
+    <cfRule type="expression" dxfId="34" priority="100">
       <formula>NOT(_xlfn.ISFORMULA(Q28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT28:AU28">
-    <cfRule type="expression" dxfId="31" priority="95">
+    <cfRule type="expression" dxfId="33" priority="95">
       <formula>NOT(_xlfn.ISFORMULA(AT28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX28:AY28">
-    <cfRule type="expression" dxfId="30" priority="97">
+    <cfRule type="expression" dxfId="32" priority="97">
       <formula>NOT(_xlfn.ISFORMULA(AX28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GC28 GF28:GG28">
-    <cfRule type="cellIs" dxfId="29" priority="89" operator="equal">
-      <formula>"INTEGER_1"</formula>
+    <cfRule type="cellIs" dxfId="31" priority="85" operator="equal">
+      <formula>"INTEGER_5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="86" operator="equal">
+      <formula>"INTEGER_4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="87" operator="equal">
+      <formula>"INTEGER_3"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="28" priority="88" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="87" operator="equal">
-      <formula>"INTEGER_3"</formula>
+    <cfRule type="cellIs" dxfId="27" priority="89" operator="equal">
+      <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="86" operator="equal">
-      <formula>"INTEGER_4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="85" operator="equal">
-      <formula>"INTEGER_5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="90" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GK28">
-    <cfRule type="cellIs" dxfId="23" priority="66" operator="equal">
-      <formula>"INTEGER_0"</formula>
+    <cfRule type="cellIs" dxfId="25" priority="61" operator="equal">
+      <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="62" operator="equal">
+      <formula>"INTEGER_4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="63" operator="equal">
+      <formula>"INTEGER_3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="64" operator="equal">
+      <formula>"INTEGER_2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="65" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="64" operator="equal">
-      <formula>"INTEGER_2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="63" operator="equal">
-      <formula>"INTEGER_3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="62" operator="equal">
-      <formula>"INTEGER_4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="61" operator="equal">
-      <formula>"INTEGER_5"</formula>
+    <cfRule type="cellIs" dxfId="20" priority="66" operator="equal">
+      <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GN28">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="43" operator="equal">
+      <formula>"INTEGER_5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="44" operator="equal">
+      <formula>"INTEGER_4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="45" operator="equal">
+      <formula>"INTEGER_3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="46" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="47" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="48" operator="equal">
       <formula>"INTEGER_0"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="43" operator="equal">
-      <formula>"INTEGER_5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="44" operator="equal">
-      <formula>"INTEGER_4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="45" operator="equal">
-      <formula>"INTEGER_3"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GP28:GR28">
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+      <formula>"INTEGER_5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+      <formula>"INTEGER_4"</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="11" priority="21" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
-      <formula>"INTEGER_4"</formula>
+    <cfRule type="cellIs" dxfId="10" priority="22" operator="equal">
+      <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="19" operator="equal">
-      <formula>"INTEGER_5"</formula>
+    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
+      <formula>"INTEGER_1"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="GT28:HD28 HF28 HH28:HM28">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"INTEGER_5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"INTEGER_4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"INTEGER_3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"INTEGER_2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
-      <formula>"INTEGER_2"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="GT28:HD28 HF28 HH28:HK28">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"INTEGER_0"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"INTEGER_1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"INTEGER_2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"INTEGER_3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"INTEGER_4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"INTEGER_5"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17344,41 +17655,41 @@
   <sheetData>
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="269" t="s">
+      <c r="B2" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="270"/>
-      <c r="D2" s="270"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="270"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="270"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="270"/>
-      <c r="K2" s="270"/>
-      <c r="L2" s="270"/>
-      <c r="M2" s="270"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="270"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="270"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="270"/>
-      <c r="U2" s="270"/>
-      <c r="V2" s="270"/>
-      <c r="W2" s="270"/>
-      <c r="X2" s="270"/>
-      <c r="Y2" s="270"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="270"/>
-      <c r="AB2" s="270"/>
-      <c r="AC2" s="270"/>
-      <c r="AD2" s="270"/>
-      <c r="AE2" s="270"/>
-      <c r="AF2" s="270"/>
-      <c r="AG2" s="270"/>
-      <c r="AH2" s="281"/>
+      <c r="C2" s="231"/>
+      <c r="D2" s="231"/>
+      <c r="E2" s="231"/>
+      <c r="F2" s="231"/>
+      <c r="G2" s="231"/>
+      <c r="H2" s="231"/>
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="231"/>
+      <c r="S2" s="231"/>
+      <c r="T2" s="231"/>
+      <c r="U2" s="231"/>
+      <c r="V2" s="231"/>
+      <c r="W2" s="231"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="231"/>
+      <c r="Z2" s="231"/>
+      <c r="AA2" s="231"/>
+      <c r="AB2" s="231"/>
+      <c r="AC2" s="231"/>
+      <c r="AD2" s="231"/>
+      <c r="AE2" s="231"/>
+      <c r="AF2" s="231"/>
+      <c r="AG2" s="231"/>
+      <c r="AH2" s="242"/>
     </row>
     <row r="3" spans="2:34" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="44" t="s">
@@ -18801,49 +19112,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="282" t="s">
+      <c r="B1" s="243" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="282"/>
-      <c r="D1" s="282"/>
-      <c r="E1" s="282"/>
-      <c r="F1" s="282"/>
-      <c r="G1" s="282"/>
-      <c r="H1" s="282"/>
-      <c r="I1" s="282"/>
-      <c r="J1" s="282"/>
-      <c r="K1" s="282"/>
-      <c r="L1" s="282"/>
-      <c r="M1" s="282"/>
-      <c r="N1" s="282"/>
-      <c r="O1" s="282"/>
-      <c r="P1" s="282"/>
-      <c r="Q1" s="282"/>
-      <c r="R1" s="282"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="243"/>
+      <c r="N1" s="243"/>
+      <c r="O1" s="243"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
     </row>
     <row r="2" spans="1:18" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24"/>
       <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="283" t="s">
+      <c r="C2" s="244" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="283"/>
-      <c r="I2" s="283"/>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
-      <c r="L2" s="283"/>
-      <c r="M2" s="283"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="283"/>
-      <c r="P2" s="283"/>
-      <c r="Q2" s="283"/>
-      <c r="R2" s="284"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="244"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="M2" s="244"/>
+      <c r="N2" s="244"/>
+      <c r="O2" s="244"/>
+      <c r="P2" s="244"/>
+      <c r="Q2" s="244"/>
+      <c r="R2" s="245"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
@@ -19293,7 +19604,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43AF4D7D-6E66-4BDD-B569-46F1C33B4B46}">
-  <dimension ref="C1:H51"/>
+  <dimension ref="C1:H59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -19302,38 +19613,38 @@
   <sheetData>
     <row r="1" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="285" t="s">
-        <v>417</v>
-      </c>
-      <c r="D2" s="286"/>
-      <c r="E2" s="286"/>
-      <c r="F2" s="286"/>
-      <c r="G2" s="286"/>
-      <c r="H2" s="287"/>
+      <c r="C2" s="246" t="s">
+        <v>414</v>
+      </c>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="108" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="108" t="s">
+        <v>416</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>417</v>
+      </c>
+      <c r="F3" s="108" t="s">
         <v>418</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="G3" s="108" t="s">
         <v>419</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="H3" s="108" t="s">
         <v>420</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>421</v>
-      </c>
-      <c r="G3" s="108" t="s">
-        <v>422</v>
-      </c>
-      <c r="H3" s="108" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="152" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D4" s="153">
         <v>0</v>
@@ -19353,7 +19664,7 @@
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" s="152" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D5" s="153">
         <v>0</v>
@@ -19373,7 +19684,7 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" s="152" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D6" s="153">
         <v>0</v>
@@ -19393,7 +19704,7 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" s="152" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D7" s="153">
         <v>0</v>
@@ -19413,7 +19724,7 @@
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="152" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D8" s="153">
         <v>0</v>
@@ -19433,7 +19744,7 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="152" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D9" s="153">
         <v>0</v>
@@ -19453,7 +19764,7 @@
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="152" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D10" s="153">
         <v>0</v>
@@ -19473,7 +19784,7 @@
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="152" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D11" s="153">
         <v>0</v>
@@ -19493,7 +19804,7 @@
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="152" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D12" s="153">
         <v>0</v>
@@ -19513,7 +19824,7 @@
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" s="152" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D13" s="153">
         <v>0</v>
@@ -19533,7 +19844,7 @@
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" s="152" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D14" s="153">
         <v>0</v>
@@ -19553,7 +19864,7 @@
     </row>
     <row r="15" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C15" s="152" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D15" s="153">
         <v>0</v>
@@ -19573,7 +19884,7 @@
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="152" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D16" s="153">
         <v>0</v>
@@ -19593,7 +19904,7 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="152" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D17" s="153">
         <v>0</v>
@@ -19613,7 +19924,7 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="152" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D18" s="153">
         <v>0</v>
@@ -19633,7 +19944,7 @@
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="152" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D19" s="153">
         <v>0</v>
@@ -19653,7 +19964,7 @@
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="152" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D20" s="153">
         <v>0</v>
@@ -19673,7 +19984,7 @@
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="152" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D21" s="153">
         <v>0</v>
@@ -19693,7 +20004,7 @@
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" s="152" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D22" s="153">
         <v>0</v>
@@ -19713,7 +20024,7 @@
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="152" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D23" s="153">
         <v>0</v>
@@ -19733,7 +20044,7 @@
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="152" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D24" s="153">
         <v>0</v>
@@ -19753,7 +20064,7 @@
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C25" s="152" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D25" s="153">
         <v>0</v>
@@ -19773,7 +20084,7 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" s="152" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D26" s="153">
         <v>0</v>
@@ -19793,7 +20104,7 @@
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C27" s="152" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D27" s="153">
         <v>0</v>
@@ -19813,7 +20124,7 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="152" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D28" s="153">
         <v>0</v>
@@ -19833,7 +20144,7 @@
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C29" s="152" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D29" s="153">
         <v>0</v>
@@ -19853,7 +20164,7 @@
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="152" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D30" s="153">
         <v>0</v>
@@ -19873,7 +20184,7 @@
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="152" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D31" s="153">
         <v>0</v>
@@ -19893,7 +20204,7 @@
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="152" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D32" s="153">
         <v>0</v>
@@ -19913,7 +20224,7 @@
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="152" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D33" s="153">
         <v>0</v>
@@ -19933,7 +20244,7 @@
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C34" s="152" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D34" s="153">
         <v>0</v>
@@ -19953,13 +20264,13 @@
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" s="152" t="s">
-        <v>522</v>
+        <v>652</v>
       </c>
       <c r="D35" s="153">
         <v>0</v>
       </c>
       <c r="E35" s="153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="153">
         <v>1</v>
@@ -19968,12 +20279,12 @@
         <v>1</v>
       </c>
       <c r="H35" s="153">
-        <v>4.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C36" s="152" t="s">
-        <v>523</v>
+        <v>653</v>
       </c>
       <c r="D36" s="153">
         <v>0</v>
@@ -19988,12 +20299,12 @@
         <v>1</v>
       </c>
       <c r="H36" s="153">
-        <v>4.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C37" s="152" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D37" s="153">
         <v>0</v>
@@ -20013,7 +20324,7 @@
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C38" s="152" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D38" s="153">
         <v>0</v>
@@ -20033,7 +20344,7 @@
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C39" s="152" t="s">
-        <v>566</v>
+        <v>521</v>
       </c>
       <c r="D39" s="153">
         <v>0</v>
@@ -20053,7 +20364,7 @@
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C40" s="152" t="s">
-        <v>567</v>
+        <v>522</v>
       </c>
       <c r="D40" s="153">
         <v>0</v>
@@ -20073,7 +20384,7 @@
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C41" s="152" t="s">
-        <v>613</v>
+        <v>563</v>
       </c>
       <c r="D41" s="153">
         <v>0</v>
@@ -20093,7 +20404,7 @@
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C42" s="152" t="s">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="D42" s="153">
         <v>0</v>
@@ -20113,7 +20424,7 @@
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C43" s="152" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D43" s="153">
         <v>0</v>
@@ -20133,7 +20444,7 @@
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C44" s="152" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D44" s="153">
         <v>0</v>
@@ -20153,7 +20464,7 @@
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C45" s="152" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="D45" s="153">
         <v>0</v>
@@ -20173,7 +20484,7 @@
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C46" s="152" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="D46" s="153">
         <v>0</v>
@@ -20193,7 +20504,7 @@
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C47" s="152" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="D47" s="153">
         <v>0</v>
@@ -20213,7 +20524,7 @@
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C48" s="152" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D48" s="153">
         <v>0</v>
@@ -20233,7 +20544,7 @@
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" s="152" t="s">
-        <v>621</v>
+        <v>656</v>
       </c>
       <c r="D49" s="153">
         <v>0</v>
@@ -20253,7 +20564,7 @@
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" s="152" t="s">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="D50" s="153">
         <v>0</v>
@@ -20273,13 +20584,13 @@
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" s="152" t="s">
-        <v>426</v>
+        <v>658</v>
       </c>
       <c r="D51" s="153">
         <v>0</v>
       </c>
       <c r="E51" s="153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="153">
         <v>1</v>
@@ -20288,6 +20599,166 @@
         <v>1</v>
       </c>
       <c r="H51" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C52" s="152" t="s">
+        <v>659</v>
+      </c>
+      <c r="D52" s="153">
+        <v>0</v>
+      </c>
+      <c r="E52" s="153">
+        <v>35</v>
+      </c>
+      <c r="F52" s="153">
+        <v>1</v>
+      </c>
+      <c r="G52" s="153">
+        <v>1</v>
+      </c>
+      <c r="H52" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C53" s="152" t="s">
+        <v>614</v>
+      </c>
+      <c r="D53" s="153">
+        <v>0</v>
+      </c>
+      <c r="E53" s="153">
+        <v>2</v>
+      </c>
+      <c r="F53" s="153">
+        <v>1</v>
+      </c>
+      <c r="G53" s="153">
+        <v>1</v>
+      </c>
+      <c r="H53" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C54" s="152" t="s">
+        <v>615</v>
+      </c>
+      <c r="D54" s="153">
+        <v>0</v>
+      </c>
+      <c r="E54" s="153">
+        <v>35</v>
+      </c>
+      <c r="F54" s="153">
+        <v>1</v>
+      </c>
+      <c r="G54" s="153">
+        <v>1</v>
+      </c>
+      <c r="H54" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C55" s="152" t="s">
+        <v>616</v>
+      </c>
+      <c r="D55" s="153">
+        <v>0</v>
+      </c>
+      <c r="E55" s="153">
+        <v>2</v>
+      </c>
+      <c r="F55" s="153">
+        <v>1</v>
+      </c>
+      <c r="G55" s="153">
+        <v>1</v>
+      </c>
+      <c r="H55" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C56" s="152" t="s">
+        <v>617</v>
+      </c>
+      <c r="D56" s="153">
+        <v>0</v>
+      </c>
+      <c r="E56" s="153">
+        <v>35</v>
+      </c>
+      <c r="F56" s="153">
+        <v>1</v>
+      </c>
+      <c r="G56" s="153">
+        <v>1</v>
+      </c>
+      <c r="H56" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C57" s="152" t="s">
+        <v>618</v>
+      </c>
+      <c r="D57" s="153">
+        <v>0</v>
+      </c>
+      <c r="E57" s="153">
+        <v>2</v>
+      </c>
+      <c r="F57" s="153">
+        <v>1</v>
+      </c>
+      <c r="G57" s="153">
+        <v>1</v>
+      </c>
+      <c r="H57" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C58" s="152" t="s">
+        <v>619</v>
+      </c>
+      <c r="D58" s="153">
+        <v>0</v>
+      </c>
+      <c r="E58" s="153">
+        <v>35</v>
+      </c>
+      <c r="F58" s="153">
+        <v>1</v>
+      </c>
+      <c r="G58" s="153">
+        <v>1</v>
+      </c>
+      <c r="H58" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C59" s="152" t="s">
+        <v>423</v>
+      </c>
+      <c r="D59" s="153">
+        <v>0</v>
+      </c>
+      <c r="E59" s="153">
+        <v>0</v>
+      </c>
+      <c r="F59" s="153">
+        <v>1</v>
+      </c>
+      <c r="G59" s="153">
+        <v>1</v>
+      </c>
+      <c r="H59" s="153">
         <v>0</v>
       </c>
     </row>
@@ -20310,50 +20781,50 @@
   <sheetData>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -20374,7 +20845,7 @@
         <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -20432,7 +20903,7 @@
         <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -20440,140 +20911,140 @@
         <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I7" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K27" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="K28" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="K29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K30" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="K31" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K32" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J33" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K33" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K34" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="35" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J35" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K35" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K36" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J37" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="K37" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J38" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K38" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J39" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K39" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J40" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K40" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="41" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J41" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -20603,7 +21074,7 @@
         <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -20611,7 +21082,7 @@
         <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -20672,15 +21143,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="D3" s="289" t="s">
-        <v>316</v>
-      </c>
-      <c r="E3" s="289"/>
-      <c r="F3" s="289"/>
+      <c r="D3" s="250" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="250"/>
+      <c r="F3" s="250"/>
     </row>
     <row r="4" spans="1:76" x14ac:dyDescent="0.25">
       <c r="D4" s="63" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E4" s="64"/>
       <c r="F4" s="66" t="s">
@@ -20995,129 +21466,129 @@
     </row>
     <row r="8" spans="1:76" ht="135" x14ac:dyDescent="0.25">
       <c r="B8" s="209"/>
-      <c r="C8" s="288" t="s">
+      <c r="C8" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="288"/>
-      <c r="E8" s="288"/>
-      <c r="F8" s="290" t="s">
+      <c r="D8" s="249"/>
+      <c r="E8" s="249"/>
+      <c r="F8" s="251" t="s">
+        <v>320</v>
+      </c>
+      <c r="G8" s="251"/>
+      <c r="H8" s="251"/>
+      <c r="I8" s="249" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="249"/>
+      <c r="K8" s="249"/>
+      <c r="L8" s="249" t="s">
+        <v>178</v>
+      </c>
+      <c r="M8" s="249"/>
+      <c r="N8" s="249"/>
+      <c r="O8" s="249" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" s="249"/>
+      <c r="Q8" s="249"/>
+      <c r="R8" s="249" t="s">
+        <v>179</v>
+      </c>
+      <c r="S8" s="249"/>
+      <c r="T8" s="249"/>
+      <c r="U8" s="249" t="s">
+        <v>166</v>
+      </c>
+      <c r="V8" s="249"/>
+      <c r="W8" s="249"/>
+      <c r="X8" s="249" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y8" s="249"/>
+      <c r="Z8" s="249"/>
+      <c r="AA8" s="249" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB8" s="249"/>
+      <c r="AC8" s="249"/>
+      <c r="AD8" s="249" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE8" s="249"/>
+      <c r="AF8" s="249"/>
+      <c r="AG8" s="249" t="s">
+        <v>372</v>
+      </c>
+      <c r="AH8" s="249"/>
+      <c r="AI8" s="249"/>
+      <c r="AJ8" s="249" t="s">
+        <v>591</v>
+      </c>
+      <c r="AK8" s="249"/>
+      <c r="AL8" s="249"/>
+      <c r="AM8" s="249" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN8" s="249"/>
+      <c r="AO8" s="249"/>
+      <c r="AP8" s="99" t="s">
+        <v>411</v>
+      </c>
+      <c r="AQ8" s="249" t="s">
+        <v>627</v>
+      </c>
+      <c r="AR8" s="249"/>
+      <c r="AS8" s="249"/>
+      <c r="AT8" s="80" t="s">
+        <v>322</v>
+      </c>
+      <c r="AU8" s="80" t="s">
+        <v>462</v>
+      </c>
+      <c r="AV8" s="80" t="s">
+        <v>463</v>
+      </c>
+      <c r="AW8" s="80" t="s">
+        <v>464</v>
+      </c>
+      <c r="AX8" s="80" t="s">
+        <v>586</v>
+      </c>
+      <c r="AY8" s="83" t="s">
+        <v>377</v>
+      </c>
+      <c r="AZ8" s="83" t="s">
+        <v>378</v>
+      </c>
+      <c r="BA8" s="83" t="s">
+        <v>379</v>
+      </c>
+      <c r="BB8" s="86" t="s">
+        <v>380</v>
+      </c>
+      <c r="BC8" s="80" t="s">
         <v>323</v>
       </c>
-      <c r="G8" s="290"/>
-      <c r="H8" s="290"/>
-      <c r="I8" s="288" t="s">
-        <v>165</v>
-      </c>
-      <c r="J8" s="288"/>
-      <c r="K8" s="288"/>
-      <c r="L8" s="288" t="s">
-        <v>178</v>
-      </c>
-      <c r="M8" s="288"/>
-      <c r="N8" s="288"/>
-      <c r="O8" s="288" t="s">
-        <v>7</v>
-      </c>
-      <c r="P8" s="288"/>
-      <c r="Q8" s="288"/>
-      <c r="R8" s="288" t="s">
-        <v>179</v>
-      </c>
-      <c r="S8" s="288"/>
-      <c r="T8" s="288"/>
-      <c r="U8" s="288" t="s">
-        <v>166</v>
-      </c>
-      <c r="V8" s="288"/>
-      <c r="W8" s="288"/>
-      <c r="X8" s="288" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y8" s="288"/>
-      <c r="Z8" s="288"/>
-      <c r="AA8" s="288" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB8" s="288"/>
-      <c r="AC8" s="288"/>
-      <c r="AD8" s="288" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE8" s="288"/>
-      <c r="AF8" s="288"/>
-      <c r="AG8" s="288" t="s">
-        <v>375</v>
-      </c>
-      <c r="AH8" s="288"/>
-      <c r="AI8" s="288"/>
-      <c r="AJ8" s="288" t="s">
-        <v>594</v>
-      </c>
-      <c r="AK8" s="288"/>
-      <c r="AL8" s="288"/>
-      <c r="AM8" s="288" t="s">
-        <v>590</v>
-      </c>
-      <c r="AN8" s="288"/>
-      <c r="AO8" s="288"/>
-      <c r="AP8" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="AQ8" s="288" t="s">
-        <v>632</v>
-      </c>
-      <c r="AR8" s="288"/>
-      <c r="AS8" s="288"/>
-      <c r="AT8" s="80" t="s">
-        <v>325</v>
-      </c>
-      <c r="AU8" s="80" t="s">
-        <v>465</v>
-      </c>
-      <c r="AV8" s="80" t="s">
-        <v>466</v>
-      </c>
-      <c r="AW8" s="80" t="s">
-        <v>467</v>
-      </c>
-      <c r="AX8" s="80" t="s">
-        <v>589</v>
-      </c>
-      <c r="AY8" s="83" t="s">
-        <v>380</v>
-      </c>
-      <c r="AZ8" s="83" t="s">
-        <v>381</v>
-      </c>
-      <c r="BA8" s="83" t="s">
-        <v>382</v>
-      </c>
-      <c r="BB8" s="86" t="s">
-        <v>383</v>
-      </c>
-      <c r="BC8" s="80" t="s">
-        <v>326</v>
-      </c>
       <c r="BD8" s="80" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="BE8" s="78" t="s">
         <v>185</v>
       </c>
       <c r="BF8" s="79" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="BG8" s="93" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="BH8" s="93" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="BI8" s="86" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="BJ8" s="92" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="BK8" s="78" t="s">
         <v>186</v>
@@ -21129,30 +21600,30 @@
         <v>188</v>
       </c>
       <c r="BN8" s="78" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="BO8" s="217" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="BP8" s="93" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="BQ8" s="218"/>
       <c r="BR8" s="218"/>
       <c r="BS8" s="220" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="BT8" s="220" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="BU8" s="220" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="BV8" s="220" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="BW8" s="220" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:76" x14ac:dyDescent="0.25">
@@ -21405,17 +21876,17 @@
       <c r="D11" s="48"/>
       <c r="E11" s="88"/>
       <c r="F11" s="50" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G11" s="48"/>
       <c r="H11" s="49"/>
       <c r="I11" s="50" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J11" s="48"/>
       <c r="K11" s="88"/>
       <c r="L11" s="50" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="88"/>
@@ -21425,7 +21896,7 @@
       <c r="P11" s="48"/>
       <c r="Q11" s="49"/>
       <c r="R11" s="50" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="S11" s="48"/>
       <c r="T11" s="88"/>
@@ -21450,25 +21921,25 @@
       <c r="AE11" s="48"/>
       <c r="AF11" s="49"/>
       <c r="AG11" s="50" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AH11" s="48"/>
       <c r="AI11" s="49"/>
       <c r="AJ11" s="50" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="AK11" s="48"/>
       <c r="AL11" s="49"/>
       <c r="AM11" s="50" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AN11" s="48"/>
       <c r="AO11" s="88"/>
       <c r="AP11" s="48" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AQ11" s="50" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="AR11" s="48"/>
       <c r="AS11" s="88"/>
@@ -21630,14 +22101,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="C1" s="241" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="241"/>
+      <c r="C1" s="252" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1" s="252"/>
     </row>
     <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C2" s="97" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D2" s="97">
         <v>1</v>
@@ -21645,7 +22116,7 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C3" s="97" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D3" s="97">
         <f>D2</f>
@@ -21657,21 +22128,21 @@
         <v>165</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C7" s="1">
         <f>'&lt;zalldev&gt;EXPORT'!BT11</f>

--- a/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
+++ b/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcad\cad\data\preload\xlsxtemplates\modelinxlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E42F043-C78E-4299-85AC-A5237A99185D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1AD21C-FF00-4C83-92DA-F87542704E55}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19920" yWindow="1260" windowWidth="29070" windowHeight="19290" tabRatio="643" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" tabRatio="643" firstSheet="1" activeTab="18" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="4" r:id="rId1"/>
@@ -794,7 +794,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="666">
   <si>
     <t>&lt;zlight&gt;</t>
   </si>
@@ -4999,47 +4999,120 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5049,105 +5122,32 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5157,28 +5157,6 @@
     <cellStyle name="Обычный_расчет нагрузки" xfId="1" xr:uid="{2A78680A-EF87-4AAC-8D9D-BEC6B0A95A74}"/>
   </cellStyles>
   <dxfs count="50">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC89D7D"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC89D7D"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5407,6 +5385,28 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC89D7D"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC89D7D"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12469,12 +12469,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O23">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O22">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13888,27 +13888,27 @@
       </c>
     </row>
     <row r="4" spans="4:57" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="259" t="s">
+      <c r="D4" s="291" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
       <c r="I4" s="62" t="s">
         <v>309</v>
       </c>
       <c r="J4" s="89"/>
       <c r="K4" s="89"/>
       <c r="P4" s="62"/>
-      <c r="Q4" s="259" t="s">
+      <c r="Q4" s="291" t="s">
         <v>308</v>
       </c>
-      <c r="R4" s="259"/>
-      <c r="S4" s="259"/>
-      <c r="T4" s="259"/>
-      <c r="U4" s="259"/>
-      <c r="V4" s="259"/>
+      <c r="R4" s="291"/>
+      <c r="S4" s="291"/>
+      <c r="T4" s="291"/>
+      <c r="U4" s="291"/>
+      <c r="V4" s="291"/>
       <c r="Z4" s="252" t="s">
         <v>428</v>
       </c>
@@ -13941,12 +13941,12 @@
       </c>
     </row>
     <row r="5" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D5" s="260" t="s">
+      <c r="D5" s="292" t="s">
         <v>307</v>
       </c>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
+      <c r="E5" s="292"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="292"/>
       <c r="H5" s="98">
         <f>AU5</f>
         <v>0</v>
@@ -13961,17 +13961,17 @@
       <c r="P5" s="61" t="s">
         <v>305</v>
       </c>
-      <c r="Q5" s="261" t="s">
+      <c r="Q5" s="293" t="s">
         <v>304</v>
       </c>
-      <c r="R5" s="261"/>
-      <c r="S5" s="261"/>
-      <c r="T5" s="261"/>
-      <c r="U5" s="261">
+      <c r="R5" s="293"/>
+      <c r="S5" s="293"/>
+      <c r="T5" s="293"/>
+      <c r="U5" s="293">
         <f ca="1">ROUNDUP(SUM($AC$26:$AC$900000),2)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="261"/>
+      <c r="V5" s="293"/>
       <c r="Z5" s="97" t="s">
         <v>416</v>
       </c>
@@ -14020,12 +14020,12 @@
       </c>
     </row>
     <row r="6" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D6" s="262" t="s">
+      <c r="D6" s="294" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="262"/>
-      <c r="F6" s="262"/>
-      <c r="G6" s="262"/>
+      <c r="E6" s="294"/>
+      <c r="F6" s="294"/>
+      <c r="G6" s="294"/>
       <c r="H6" s="88" t="s">
         <v>435</v>
       </c>
@@ -14040,17 +14040,17 @@
       <c r="P6" s="61">
         <v>63</v>
       </c>
-      <c r="Q6" s="261" t="s">
+      <c r="Q6" s="293" t="s">
         <v>301</v>
       </c>
-      <c r="R6" s="261"/>
-      <c r="S6" s="261"/>
-      <c r="T6" s="261"/>
-      <c r="U6" s="261">
+      <c r="R6" s="293"/>
+      <c r="S6" s="293"/>
+      <c r="T6" s="293"/>
+      <c r="U6" s="293">
         <f ca="1">ROUNDUP(U5*U11,2)</f>
         <v>0</v>
       </c>
-      <c r="V6" s="261"/>
+      <c r="V6" s="293"/>
       <c r="Z6" s="97" t="s">
         <v>417</v>
       </c>
@@ -14059,12 +14059,12 @@
       </c>
     </row>
     <row r="7" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D7" s="255" t="s">
+      <c r="D7" s="286" t="s">
         <v>300</v>
       </c>
-      <c r="E7" s="255"/>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="286"/>
       <c r="H7" s="58">
         <v>45399</v>
       </c>
@@ -14079,25 +14079,25 @@
       <c r="P7" s="61">
         <v>32</v>
       </c>
-      <c r="Q7" s="261" t="s">
+      <c r="Q7" s="293" t="s">
         <v>299</v>
       </c>
-      <c r="R7" s="261"/>
-      <c r="S7" s="261"/>
-      <c r="T7" s="261"/>
-      <c r="U7" s="261" t="e">
+      <c r="R7" s="293"/>
+      <c r="S7" s="293"/>
+      <c r="T7" s="293"/>
+      <c r="U7" s="293" t="e">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!C4:C5,MATCH(H11,BD!B4:B5,0))*U8),2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V7" s="261"/>
+      <c r="V7" s="293"/>
     </row>
     <row r="8" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D8" s="255" t="s">
+      <c r="D8" s="286" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="255"/>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
       <c r="H8" s="58" t="s">
         <v>297</v>
       </c>
@@ -14112,25 +14112,25 @@
       <c r="P8" s="61">
         <v>6</v>
       </c>
-      <c r="Q8" s="263" t="s">
+      <c r="Q8" s="295" t="s">
         <v>296</v>
       </c>
-      <c r="R8" s="264"/>
-      <c r="S8" s="264"/>
-      <c r="T8" s="265"/>
-      <c r="U8" s="268" t="e">
+      <c r="R8" s="296"/>
+      <c r="S8" s="296"/>
+      <c r="T8" s="297"/>
+      <c r="U8" s="284" t="e">
         <f ca="1">ROUNDUP(SUM(AC28:AC777777)/SUM(AG28:AG777777),2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V8" s="268"/>
+      <c r="V8" s="284"/>
     </row>
     <row r="9" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D9" s="255" t="s">
+      <c r="D9" s="286" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="255"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
       <c r="H9" s="58" t="s">
         <v>294</v>
       </c>
@@ -14145,22 +14145,22 @@
       <c r="P9" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="Q9" s="256" t="s">
+      <c r="Q9" s="298" t="s">
         <v>292</v>
       </c>
-      <c r="R9" s="256"/>
-      <c r="S9" s="256"/>
-      <c r="T9" s="256"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
+      <c r="R9" s="298"/>
+      <c r="S9" s="298"/>
+      <c r="T9" s="298"/>
+      <c r="U9" s="299"/>
+      <c r="V9" s="299"/>
     </row>
     <row r="10" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D10" s="255" t="s">
+      <c r="D10" s="286" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="255"/>
-      <c r="F10" s="255"/>
-      <c r="G10" s="255"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="286"/>
       <c r="I10" s="61" t="s">
         <v>290</v>
       </c>
@@ -14169,20 +14169,20 @@
       <c r="P10" s="61">
         <v>4</v>
       </c>
-      <c r="Q10" s="256"/>
-      <c r="R10" s="256"/>
-      <c r="S10" s="256"/>
-      <c r="T10" s="256"/>
-      <c r="U10" s="257"/>
-      <c r="V10" s="257"/>
+      <c r="Q10" s="298"/>
+      <c r="R10" s="298"/>
+      <c r="S10" s="298"/>
+      <c r="T10" s="298"/>
+      <c r="U10" s="299"/>
+      <c r="V10" s="299"/>
     </row>
     <row r="11" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D11" s="255" t="s">
+      <c r="D11" s="286" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="255"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
+      <c r="E11" s="286"/>
+      <c r="F11" s="286"/>
+      <c r="G11" s="286"/>
       <c r="H11" s="97">
         <v>380</v>
       </c>
@@ -14194,24 +14194,24 @@
       <c r="P11" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="Q11" s="281" t="s">
+      <c r="Q11" s="277" t="s">
         <v>286</v>
       </c>
-      <c r="R11" s="282"/>
-      <c r="S11" s="282"/>
-      <c r="T11" s="283"/>
-      <c r="U11" s="284">
+      <c r="R11" s="278"/>
+      <c r="S11" s="278"/>
+      <c r="T11" s="279"/>
+      <c r="U11" s="280">
         <v>1</v>
       </c>
-      <c r="V11" s="285"/>
+      <c r="V11" s="281"/>
     </row>
     <row r="12" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D12" s="255" t="s">
+      <c r="D12" s="286" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="255"/>
-      <c r="F12" s="255"/>
-      <c r="G12" s="255"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="286"/>
+      <c r="G12" s="286"/>
       <c r="H12" s="58" t="s">
         <v>284</v>
       </c>
@@ -14223,99 +14223,99 @@
       <c r="P12" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="258" t="s">
+      <c r="Q12" s="287" t="s">
         <v>282</v>
       </c>
-      <c r="R12" s="258"/>
-      <c r="S12" s="258"/>
-      <c r="T12" s="258"/>
-      <c r="U12" s="258">
+      <c r="R12" s="287"/>
+      <c r="S12" s="287"/>
+      <c r="T12" s="287"/>
+      <c r="U12" s="287">
         <v>44.5</v>
       </c>
-      <c r="V12" s="258"/>
+      <c r="V12" s="287"/>
     </row>
     <row r="13" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D13" s="255" t="s">
+      <c r="D13" s="286" t="s">
         <v>281</v>
       </c>
-      <c r="E13" s="255"/>
-      <c r="F13" s="255"/>
-      <c r="G13" s="255"/>
+      <c r="E13" s="286"/>
+      <c r="F13" s="286"/>
+      <c r="G13" s="286"/>
       <c r="H13" s="58" t="s">
         <v>280</v>
       </c>
       <c r="I13" s="59"/>
       <c r="P13" s="59"/>
-      <c r="Q13" s="258" t="s">
+      <c r="Q13" s="287" t="s">
         <v>279</v>
       </c>
-      <c r="R13" s="258"/>
-      <c r="S13" s="258"/>
-      <c r="T13" s="258"/>
-      <c r="U13" s="258">
+      <c r="R13" s="287"/>
+      <c r="S13" s="287"/>
+      <c r="T13" s="287"/>
+      <c r="U13" s="287">
         <v>44.5</v>
       </c>
-      <c r="V13" s="258"/>
+      <c r="V13" s="287"/>
     </row>
     <row r="14" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D14" s="255" t="s">
+      <c r="D14" s="286" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="255"/>
-      <c r="F14" s="255"/>
-      <c r="G14" s="255"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
       <c r="H14" s="60" t="str">
         <f>'&lt;zlight&gt;'!G20&amp;"."&amp;'&lt;zlight&gt;'!H20</f>
         <v>.</v>
       </c>
       <c r="I14" s="59"/>
       <c r="P14" s="59"/>
-      <c r="Q14" s="258" t="s">
+      <c r="Q14" s="287" t="s">
         <v>277</v>
       </c>
-      <c r="R14" s="258"/>
-      <c r="S14" s="258"/>
-      <c r="T14" s="258"/>
-      <c r="U14" s="258">
+      <c r="R14" s="287"/>
+      <c r="S14" s="287"/>
+      <c r="T14" s="287"/>
+      <c r="U14" s="287">
         <v>44.5</v>
       </c>
-      <c r="V14" s="258"/>
+      <c r="V14" s="287"/>
     </row>
     <row r="15" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D15" s="255" t="s">
+      <c r="D15" s="286" t="s">
         <v>276</v>
       </c>
-      <c r="E15" s="255"/>
-      <c r="F15" s="255"/>
-      <c r="G15" s="255"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
       <c r="H15" s="58">
         <v>77</v>
       </c>
       <c r="P15" s="59"/>
-      <c r="Q15" s="267" t="s">
+      <c r="Q15" s="288" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="267"/>
-      <c r="S15" s="267"/>
-      <c r="T15" s="267"/>
-      <c r="U15" s="268" t="e">
+      <c r="R15" s="288"/>
+      <c r="S15" s="288"/>
+      <c r="T15" s="288"/>
+      <c r="U15" s="284" t="e">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!$C$4:$C$5,MATCH(H11,BD!$B$4:$B$5,0))*U8),2)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="V15" s="268"/>
+      <c r="V15" s="284"/>
     </row>
     <row r="16" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="Q16" s="271" t="s">
+      <c r="Q16" s="267" t="s">
         <v>398</v>
       </c>
-      <c r="R16" s="271"/>
-      <c r="S16" s="271"/>
-      <c r="T16" s="271"/>
-      <c r="U16" s="271" t="e">
+      <c r="R16" s="267"/>
+      <c r="S16" s="267"/>
+      <c r="T16" s="267"/>
+      <c r="U16" s="267" t="e">
         <f>INDEX(BB5:BB9,MATCH(1,BD5:BD9,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="V16" s="271"/>
+      <c r="V16" s="267"/>
     </row>
     <row r="22" spans="1:282" x14ac:dyDescent="0.25">
       <c r="L22" s="139" t="s">
@@ -15463,209 +15463,209 @@
       </c>
     </row>
     <row r="25" spans="1:282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BD25" s="275" t="s">
+      <c r="BD25" s="271" t="s">
         <v>506</v>
       </c>
-      <c r="BE25" s="276"/>
-      <c r="BF25" s="276"/>
-      <c r="BG25" s="276"/>
-      <c r="BH25" s="276"/>
-      <c r="BI25" s="276"/>
-      <c r="BJ25" s="276"/>
-      <c r="BK25" s="276"/>
-      <c r="BL25" s="276"/>
-      <c r="BM25" s="276"/>
-      <c r="BN25" s="276"/>
-      <c r="BO25" s="276"/>
-      <c r="BP25" s="276"/>
-      <c r="BQ25" s="276"/>
-      <c r="BR25" s="276"/>
-      <c r="BS25" s="276"/>
-      <c r="BT25" s="276"/>
-      <c r="BU25" s="276"/>
-      <c r="BV25" s="276"/>
-      <c r="BW25" s="276"/>
-      <c r="BX25" s="276"/>
-      <c r="BY25" s="276"/>
-      <c r="BZ25" s="276"/>
-      <c r="CA25" s="277"/>
-      <c r="CB25" s="275" t="s">
+      <c r="BE25" s="272"/>
+      <c r="BF25" s="272"/>
+      <c r="BG25" s="272"/>
+      <c r="BH25" s="272"/>
+      <c r="BI25" s="272"/>
+      <c r="BJ25" s="272"/>
+      <c r="BK25" s="272"/>
+      <c r="BL25" s="272"/>
+      <c r="BM25" s="272"/>
+      <c r="BN25" s="272"/>
+      <c r="BO25" s="272"/>
+      <c r="BP25" s="272"/>
+      <c r="BQ25" s="272"/>
+      <c r="BR25" s="272"/>
+      <c r="BS25" s="272"/>
+      <c r="BT25" s="272"/>
+      <c r="BU25" s="272"/>
+      <c r="BV25" s="272"/>
+      <c r="BW25" s="272"/>
+      <c r="BX25" s="272"/>
+      <c r="BY25" s="272"/>
+      <c r="BZ25" s="272"/>
+      <c r="CA25" s="273"/>
+      <c r="CB25" s="271" t="s">
         <v>509</v>
       </c>
-      <c r="CC25" s="276"/>
-      <c r="CD25" s="276"/>
-      <c r="CE25" s="276"/>
-      <c r="CF25" s="276"/>
-      <c r="CG25" s="276"/>
-      <c r="CH25" s="276"/>
-      <c r="CI25" s="276"/>
-      <c r="CJ25" s="276"/>
-      <c r="CK25" s="276"/>
-      <c r="CL25" s="276"/>
-      <c r="CM25" s="276"/>
-      <c r="CN25" s="276"/>
-      <c r="CO25" s="276"/>
-      <c r="CP25" s="276"/>
-      <c r="CQ25" s="276"/>
-      <c r="CR25" s="276"/>
-      <c r="CS25" s="276"/>
-      <c r="CT25" s="278" t="s">
+      <c r="CC25" s="272"/>
+      <c r="CD25" s="272"/>
+      <c r="CE25" s="272"/>
+      <c r="CF25" s="272"/>
+      <c r="CG25" s="272"/>
+      <c r="CH25" s="272"/>
+      <c r="CI25" s="272"/>
+      <c r="CJ25" s="272"/>
+      <c r="CK25" s="272"/>
+      <c r="CL25" s="272"/>
+      <c r="CM25" s="272"/>
+      <c r="CN25" s="272"/>
+      <c r="CO25" s="272"/>
+      <c r="CP25" s="272"/>
+      <c r="CQ25" s="272"/>
+      <c r="CR25" s="272"/>
+      <c r="CS25" s="272"/>
+      <c r="CT25" s="274" t="s">
         <v>266</v>
       </c>
-      <c r="CU25" s="279"/>
-      <c r="CV25" s="279"/>
-      <c r="CW25" s="279"/>
-      <c r="CX25" s="279"/>
-      <c r="CY25" s="279"/>
-      <c r="CZ25" s="279"/>
-      <c r="DA25" s="279"/>
-      <c r="DB25" s="279"/>
-      <c r="DC25" s="279"/>
-      <c r="DD25" s="279"/>
-      <c r="DE25" s="279"/>
-      <c r="DF25" s="279"/>
-      <c r="DG25" s="279"/>
-      <c r="DH25" s="279"/>
-      <c r="DI25" s="279"/>
-      <c r="DJ25" s="279"/>
-      <c r="DK25" s="279"/>
-      <c r="DL25" s="279"/>
-      <c r="DM25" s="279"/>
-      <c r="DN25" s="279"/>
-      <c r="DO25" s="279"/>
-      <c r="DP25" s="279"/>
-      <c r="DQ25" s="279"/>
-      <c r="DR25" s="279"/>
-      <c r="DS25" s="279"/>
-      <c r="DT25" s="279"/>
-      <c r="DU25" s="279"/>
-      <c r="DV25" s="279"/>
-      <c r="DW25" s="279"/>
-      <c r="DX25" s="279"/>
-      <c r="DY25" s="279"/>
-      <c r="DZ25" s="279"/>
-      <c r="EA25" s="279"/>
-      <c r="EB25" s="279"/>
-      <c r="EC25" s="279"/>
-      <c r="ED25" s="279"/>
-      <c r="EE25" s="279"/>
-      <c r="EF25" s="279"/>
-      <c r="EG25" s="279"/>
-      <c r="EH25" s="279"/>
-      <c r="EI25" s="279"/>
-      <c r="EJ25" s="279"/>
-      <c r="EK25" s="279"/>
-      <c r="EL25" s="279"/>
-      <c r="EM25" s="279"/>
-      <c r="EN25" s="279"/>
-      <c r="EO25" s="279"/>
-      <c r="EP25" s="279"/>
-      <c r="EQ25" s="279"/>
-      <c r="ER25" s="279"/>
-      <c r="ES25" s="279"/>
-      <c r="ET25" s="279"/>
-      <c r="EU25" s="279"/>
-      <c r="EV25" s="279"/>
-      <c r="EW25" s="279"/>
-      <c r="EX25" s="279"/>
-      <c r="EY25" s="279"/>
-      <c r="EZ25" s="279"/>
-      <c r="FA25" s="279"/>
-      <c r="FB25" s="279"/>
-      <c r="FC25" s="279"/>
-      <c r="FD25" s="279"/>
-      <c r="FE25" s="279"/>
-      <c r="FF25" s="279"/>
-      <c r="FG25" s="279"/>
-      <c r="FH25" s="279"/>
-      <c r="FI25" s="279"/>
-      <c r="FJ25" s="279"/>
-      <c r="FK25" s="279"/>
-      <c r="FL25" s="279"/>
-      <c r="FM25" s="279"/>
-      <c r="FN25" s="279"/>
-      <c r="FO25" s="279"/>
-      <c r="FP25" s="280"/>
+      <c r="CU25" s="275"/>
+      <c r="CV25" s="275"/>
+      <c r="CW25" s="275"/>
+      <c r="CX25" s="275"/>
+      <c r="CY25" s="275"/>
+      <c r="CZ25" s="275"/>
+      <c r="DA25" s="275"/>
+      <c r="DB25" s="275"/>
+      <c r="DC25" s="275"/>
+      <c r="DD25" s="275"/>
+      <c r="DE25" s="275"/>
+      <c r="DF25" s="275"/>
+      <c r="DG25" s="275"/>
+      <c r="DH25" s="275"/>
+      <c r="DI25" s="275"/>
+      <c r="DJ25" s="275"/>
+      <c r="DK25" s="275"/>
+      <c r="DL25" s="275"/>
+      <c r="DM25" s="275"/>
+      <c r="DN25" s="275"/>
+      <c r="DO25" s="275"/>
+      <c r="DP25" s="275"/>
+      <c r="DQ25" s="275"/>
+      <c r="DR25" s="275"/>
+      <c r="DS25" s="275"/>
+      <c r="DT25" s="275"/>
+      <c r="DU25" s="275"/>
+      <c r="DV25" s="275"/>
+      <c r="DW25" s="275"/>
+      <c r="DX25" s="275"/>
+      <c r="DY25" s="275"/>
+      <c r="DZ25" s="275"/>
+      <c r="EA25" s="275"/>
+      <c r="EB25" s="275"/>
+      <c r="EC25" s="275"/>
+      <c r="ED25" s="275"/>
+      <c r="EE25" s="275"/>
+      <c r="EF25" s="275"/>
+      <c r="EG25" s="275"/>
+      <c r="EH25" s="275"/>
+      <c r="EI25" s="275"/>
+      <c r="EJ25" s="275"/>
+      <c r="EK25" s="275"/>
+      <c r="EL25" s="275"/>
+      <c r="EM25" s="275"/>
+      <c r="EN25" s="275"/>
+      <c r="EO25" s="275"/>
+      <c r="EP25" s="275"/>
+      <c r="EQ25" s="275"/>
+      <c r="ER25" s="275"/>
+      <c r="ES25" s="275"/>
+      <c r="ET25" s="275"/>
+      <c r="EU25" s="275"/>
+      <c r="EV25" s="275"/>
+      <c r="EW25" s="275"/>
+      <c r="EX25" s="275"/>
+      <c r="EY25" s="275"/>
+      <c r="EZ25" s="275"/>
+      <c r="FA25" s="275"/>
+      <c r="FB25" s="275"/>
+      <c r="FC25" s="275"/>
+      <c r="FD25" s="275"/>
+      <c r="FE25" s="275"/>
+      <c r="FF25" s="275"/>
+      <c r="FG25" s="275"/>
+      <c r="FH25" s="275"/>
+      <c r="FI25" s="275"/>
+      <c r="FJ25" s="275"/>
+      <c r="FK25" s="275"/>
+      <c r="FL25" s="275"/>
+      <c r="FM25" s="275"/>
+      <c r="FN25" s="275"/>
+      <c r="FO25" s="275"/>
+      <c r="FP25" s="276"/>
     </row>
     <row r="26" spans="1:282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="269" t="s">
+      <c r="D26" s="289" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="266" t="s">
+      <c r="E26" s="259" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="266" t="s">
+      <c r="F26" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="266" t="s">
+      <c r="G26" s="259" t="s">
         <v>273</v>
       </c>
-      <c r="H26" s="266" t="s">
+      <c r="H26" s="259" t="s">
         <v>272</v>
       </c>
-      <c r="I26" s="266" t="s">
+      <c r="I26" s="259" t="s">
         <v>271</v>
       </c>
-      <c r="J26" s="290" t="s">
+      <c r="J26" s="255" t="s">
         <v>602</v>
       </c>
-      <c r="K26" s="270" t="s">
+      <c r="K26" s="290" t="s">
         <v>382</v>
       </c>
-      <c r="L26" s="293" t="s">
+      <c r="L26" s="258" t="s">
         <v>383</v>
       </c>
-      <c r="M26" s="293"/>
-      <c r="N26" s="293"/>
-      <c r="O26" s="266" t="s">
+      <c r="M26" s="258"/>
+      <c r="N26" s="258"/>
+      <c r="O26" s="259" t="s">
         <v>270</v>
       </c>
-      <c r="P26" s="294" t="s">
+      <c r="P26" s="260" t="s">
         <v>269</v>
       </c>
-      <c r="Q26" s="294"/>
-      <c r="R26" s="294"/>
-      <c r="S26" s="294"/>
-      <c r="T26" s="294"/>
-      <c r="U26" s="294"/>
-      <c r="V26" s="294"/>
-      <c r="W26" s="294"/>
-      <c r="X26" s="294"/>
-      <c r="Y26" s="294"/>
-      <c r="Z26" s="294"/>
-      <c r="AA26" s="294"/>
-      <c r="AB26" s="295" t="s">
+      <c r="Q26" s="260"/>
+      <c r="R26" s="260"/>
+      <c r="S26" s="260"/>
+      <c r="T26" s="260"/>
+      <c r="U26" s="260"/>
+      <c r="V26" s="260"/>
+      <c r="W26" s="260"/>
+      <c r="X26" s="260"/>
+      <c r="Y26" s="260"/>
+      <c r="Z26" s="260"/>
+      <c r="AA26" s="260"/>
+      <c r="AB26" s="261" t="s">
         <v>268</v>
       </c>
-      <c r="AC26" s="295"/>
-      <c r="AD26" s="295"/>
-      <c r="AE26" s="295"/>
-      <c r="AF26" s="295"/>
-      <c r="AG26" s="295"/>
-      <c r="AH26" s="295"/>
-      <c r="AI26" s="295"/>
-      <c r="AJ26" s="295"/>
-      <c r="AK26" s="295"/>
-      <c r="AL26" s="295"/>
-      <c r="AM26" s="295"/>
-      <c r="AN26" s="295" t="s">
+      <c r="AC26" s="261"/>
+      <c r="AD26" s="261"/>
+      <c r="AE26" s="261"/>
+      <c r="AF26" s="261"/>
+      <c r="AG26" s="261"/>
+      <c r="AH26" s="261"/>
+      <c r="AI26" s="261"/>
+      <c r="AJ26" s="261"/>
+      <c r="AK26" s="261"/>
+      <c r="AL26" s="261"/>
+      <c r="AM26" s="261"/>
+      <c r="AN26" s="261" t="s">
         <v>267</v>
       </c>
-      <c r="AO26" s="295"/>
-      <c r="AP26" s="295"/>
-      <c r="AQ26" s="295"/>
-      <c r="AR26" s="295"/>
-      <c r="AS26" s="295"/>
-      <c r="AT26" s="295"/>
-      <c r="AU26" s="295"/>
-      <c r="AV26" s="295"/>
-      <c r="AW26" s="295"/>
-      <c r="AX26" s="295"/>
-      <c r="AY26" s="295"/>
-      <c r="AZ26" s="295"/>
-      <c r="BA26" s="295"/>
-      <c r="BB26" s="295"/>
-      <c r="BC26" s="295"/>
+      <c r="AO26" s="261"/>
+      <c r="AP26" s="261"/>
+      <c r="AQ26" s="261"/>
+      <c r="AR26" s="261"/>
+      <c r="AS26" s="261"/>
+      <c r="AT26" s="261"/>
+      <c r="AU26" s="261"/>
+      <c r="AV26" s="261"/>
+      <c r="AW26" s="261"/>
+      <c r="AX26" s="261"/>
+      <c r="AY26" s="261"/>
+      <c r="AZ26" s="261"/>
+      <c r="BA26" s="261"/>
+      <c r="BB26" s="261"/>
+      <c r="BC26" s="261"/>
       <c r="BD26" s="59"/>
       <c r="BE26" s="59"/>
       <c r="BF26" s="59"/>
@@ -15674,26 +15674,26 @@
       <c r="BI26" s="59"/>
       <c r="BJ26" s="59"/>
       <c r="BK26" s="59"/>
-      <c r="BL26" s="297" t="s">
+      <c r="BL26" s="263" t="s">
         <v>495</v>
       </c>
-      <c r="BM26" s="297"/>
-      <c r="BN26" s="297"/>
-      <c r="BO26" s="297"/>
-      <c r="BP26" s="297"/>
-      <c r="BQ26" s="297"/>
-      <c r="BR26" s="297"/>
-      <c r="BS26" s="297"/>
+      <c r="BM26" s="263"/>
+      <c r="BN26" s="263"/>
+      <c r="BO26" s="263"/>
+      <c r="BP26" s="263"/>
+      <c r="BQ26" s="263"/>
+      <c r="BR26" s="263"/>
+      <c r="BS26" s="263"/>
       <c r="BT26" s="59"/>
       <c r="BU26" s="59"/>
       <c r="BV26" s="59"/>
-      <c r="BW26" s="298" t="s">
+      <c r="BW26" s="264" t="s">
         <v>508</v>
       </c>
-      <c r="BX26" s="298"/>
-      <c r="BY26" s="298"/>
-      <c r="BZ26" s="298"/>
-      <c r="CA26" s="298"/>
+      <c r="BX26" s="264"/>
+      <c r="BY26" s="264"/>
+      <c r="BZ26" s="264"/>
+      <c r="CA26" s="264"/>
       <c r="CB26" s="59"/>
       <c r="CC26" s="59"/>
       <c r="CD26" s="59"/>
@@ -15724,84 +15724,84 @@
       <c r="DC26" s="59"/>
       <c r="DD26" s="59"/>
       <c r="DE26" s="59"/>
-      <c r="DF26" s="287" t="s">
+      <c r="DF26" s="283" t="s">
         <v>527</v>
       </c>
-      <c r="DG26" s="287"/>
-      <c r="DH26" s="287"/>
-      <c r="DI26" s="287"/>
-      <c r="DJ26" s="287"/>
-      <c r="DK26" s="287"/>
-      <c r="DL26" s="287"/>
-      <c r="DM26" s="287"/>
-      <c r="DN26" s="287"/>
-      <c r="DO26" s="287"/>
-      <c r="DP26" s="287"/>
-      <c r="DQ26" s="287"/>
-      <c r="DR26" s="287"/>
-      <c r="DS26" s="287"/>
-      <c r="DT26" s="287"/>
-      <c r="DU26" s="287"/>
-      <c r="DV26" s="287"/>
-      <c r="DW26" s="287"/>
-      <c r="DX26" s="286" t="s">
+      <c r="DG26" s="283"/>
+      <c r="DH26" s="283"/>
+      <c r="DI26" s="283"/>
+      <c r="DJ26" s="283"/>
+      <c r="DK26" s="283"/>
+      <c r="DL26" s="283"/>
+      <c r="DM26" s="283"/>
+      <c r="DN26" s="283"/>
+      <c r="DO26" s="283"/>
+      <c r="DP26" s="283"/>
+      <c r="DQ26" s="283"/>
+      <c r="DR26" s="283"/>
+      <c r="DS26" s="283"/>
+      <c r="DT26" s="283"/>
+      <c r="DU26" s="283"/>
+      <c r="DV26" s="283"/>
+      <c r="DW26" s="283"/>
+      <c r="DX26" s="282" t="s">
         <v>206</v>
       </c>
-      <c r="DY26" s="286"/>
-      <c r="DZ26" s="286"/>
-      <c r="EA26" s="272" t="s">
+      <c r="DY26" s="282"/>
+      <c r="DZ26" s="282"/>
+      <c r="EA26" s="268" t="s">
         <v>205</v>
       </c>
-      <c r="EB26" s="273"/>
-      <c r="EC26" s="273"/>
-      <c r="ED26" s="273"/>
-      <c r="EE26" s="273"/>
-      <c r="EF26" s="273"/>
-      <c r="EG26" s="273"/>
-      <c r="EH26" s="273"/>
-      <c r="EI26" s="273"/>
-      <c r="EJ26" s="273"/>
-      <c r="EK26" s="273"/>
-      <c r="EL26" s="273"/>
-      <c r="EM26" s="273"/>
-      <c r="EN26" s="273"/>
-      <c r="EO26" s="273"/>
-      <c r="EP26" s="273"/>
-      <c r="EQ26" s="288" t="s">
+      <c r="EB26" s="269"/>
+      <c r="EC26" s="269"/>
+      <c r="ED26" s="269"/>
+      <c r="EE26" s="269"/>
+      <c r="EF26" s="269"/>
+      <c r="EG26" s="269"/>
+      <c r="EH26" s="269"/>
+      <c r="EI26" s="269"/>
+      <c r="EJ26" s="269"/>
+      <c r="EK26" s="269"/>
+      <c r="EL26" s="269"/>
+      <c r="EM26" s="269"/>
+      <c r="EN26" s="269"/>
+      <c r="EO26" s="269"/>
+      <c r="EP26" s="269"/>
+      <c r="EQ26" s="285" t="s">
         <v>204</v>
       </c>
-      <c r="ER26" s="288"/>
-      <c r="ES26" s="288"/>
-      <c r="ET26" s="288"/>
-      <c r="EU26" s="288"/>
-      <c r="EV26" s="288"/>
-      <c r="EW26" s="289" t="s">
+      <c r="ER26" s="285"/>
+      <c r="ES26" s="285"/>
+      <c r="ET26" s="285"/>
+      <c r="EU26" s="285"/>
+      <c r="EV26" s="285"/>
+      <c r="EW26" s="265" t="s">
         <v>203</v>
       </c>
-      <c r="EX26" s="289"/>
-      <c r="EY26" s="289"/>
-      <c r="EZ26" s="289"/>
-      <c r="FA26" s="289" t="s">
+      <c r="EX26" s="265"/>
+      <c r="EY26" s="265"/>
+      <c r="EZ26" s="265"/>
+      <c r="FA26" s="265" t="s">
         <v>202</v>
       </c>
-      <c r="FB26" s="289"/>
-      <c r="FC26" s="289"/>
-      <c r="FD26" s="289"/>
-      <c r="FE26" s="289" t="s">
+      <c r="FB26" s="265"/>
+      <c r="FC26" s="265"/>
+      <c r="FD26" s="265"/>
+      <c r="FE26" s="265" t="s">
         <v>201</v>
       </c>
-      <c r="FF26" s="289"/>
-      <c r="FG26" s="289"/>
-      <c r="FH26" s="289"/>
-      <c r="FI26" s="289"/>
-      <c r="FJ26" s="289"/>
-      <c r="FK26" s="289" t="s">
+      <c r="FF26" s="265"/>
+      <c r="FG26" s="265"/>
+      <c r="FH26" s="265"/>
+      <c r="FI26" s="265"/>
+      <c r="FJ26" s="265"/>
+      <c r="FK26" s="265" t="s">
         <v>200</v>
       </c>
-      <c r="FL26" s="289"/>
-      <c r="FM26" s="289"/>
-      <c r="FN26" s="289"/>
-      <c r="FO26" s="289"/>
+      <c r="FL26" s="265"/>
+      <c r="FM26" s="265"/>
+      <c r="FN26" s="265"/>
+      <c r="FO26" s="265"/>
       <c r="FP26" s="59"/>
       <c r="FQ26" s="81"/>
       <c r="FR26" s="81"/>
@@ -15886,19 +15886,33 @@
         <f>IF(J5="АВ","INTEGER_1","INTEGER_2")</f>
         <v>INTEGER_1</v>
       </c>
+      <c r="GP26" t="s">
+        <v>194</v>
+      </c>
+      <c r="GQ26" t="str">
+        <f>"фидер "&amp;AX5&amp;"."&amp;AV5</f>
+        <v>фидер 0.0</v>
+      </c>
+      <c r="GR26" t="s">
+        <v>193</v>
+      </c>
+      <c r="GS26" t="str">
+        <f>""</f>
+        <v/>
+      </c>
       <c r="HN26" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:282" ht="103.5" x14ac:dyDescent="0.25">
-      <c r="D27" s="269"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="266"/>
-      <c r="G27" s="266"/>
-      <c r="H27" s="266"/>
-      <c r="I27" s="266"/>
-      <c r="J27" s="291"/>
-      <c r="K27" s="270"/>
+      <c r="D27" s="289"/>
+      <c r="E27" s="259"/>
+      <c r="F27" s="259"/>
+      <c r="G27" s="259"/>
+      <c r="H27" s="259"/>
+      <c r="I27" s="259"/>
+      <c r="J27" s="256"/>
+      <c r="K27" s="290"/>
       <c r="L27" s="91" t="s">
         <v>257</v>
       </c>
@@ -15908,7 +15922,7 @@
       <c r="N27" s="91" t="s">
         <v>255</v>
       </c>
-      <c r="O27" s="266"/>
+      <c r="O27" s="259"/>
       <c r="P27" s="161" t="s">
         <v>326</v>
       </c>
@@ -16374,10 +16388,10 @@
       <c r="FP27" s="193" t="s">
         <v>424</v>
       </c>
-      <c r="FQ27" s="299" t="s">
+      <c r="FQ27" s="266" t="s">
         <v>585</v>
       </c>
-      <c r="FR27" s="299"/>
+      <c r="FR27" s="266"/>
       <c r="FU27" s="113">
         <f>35*$AA$5</f>
         <v>35</v>
@@ -16403,56 +16417,56 @@
       <c r="GQ27" s="104"/>
       <c r="GR27" s="104"/>
       <c r="GS27" s="104"/>
-      <c r="HO27" s="296" t="s">
+      <c r="HO27" s="262" t="s">
         <v>413</v>
       </c>
-      <c r="HP27" s="296"/>
-      <c r="HQ27" s="296"/>
-      <c r="HR27" s="296"/>
-      <c r="HS27" s="296"/>
-      <c r="HT27" s="296"/>
-      <c r="HU27" s="296"/>
-      <c r="HV27" s="296"/>
-      <c r="HW27" s="274" t="s">
+      <c r="HP27" s="262"/>
+      <c r="HQ27" s="262"/>
+      <c r="HR27" s="262"/>
+      <c r="HS27" s="262"/>
+      <c r="HT27" s="262"/>
+      <c r="HU27" s="262"/>
+      <c r="HV27" s="262"/>
+      <c r="HW27" s="270" t="s">
         <v>211</v>
       </c>
-      <c r="HX27" s="274"/>
-      <c r="HY27" s="274"/>
-      <c r="HZ27" s="274"/>
-      <c r="IA27" s="274"/>
-      <c r="IB27" s="274"/>
-      <c r="IC27" s="274"/>
-      <c r="ID27" s="274"/>
-      <c r="IE27" s="274"/>
-      <c r="IF27" s="274"/>
-      <c r="IG27" s="274"/>
-      <c r="IH27" s="274"/>
-      <c r="II27" s="274"/>
-      <c r="IJ27" s="274"/>
-      <c r="IK27" s="274"/>
-      <c r="IL27" s="274"/>
-      <c r="IM27" s="274"/>
-      <c r="IN27" s="274"/>
-      <c r="IO27" s="292" t="s">
+      <c r="HX27" s="270"/>
+      <c r="HY27" s="270"/>
+      <c r="HZ27" s="270"/>
+      <c r="IA27" s="270"/>
+      <c r="IB27" s="270"/>
+      <c r="IC27" s="270"/>
+      <c r="ID27" s="270"/>
+      <c r="IE27" s="270"/>
+      <c r="IF27" s="270"/>
+      <c r="IG27" s="270"/>
+      <c r="IH27" s="270"/>
+      <c r="II27" s="270"/>
+      <c r="IJ27" s="270"/>
+      <c r="IK27" s="270"/>
+      <c r="IL27" s="270"/>
+      <c r="IM27" s="270"/>
+      <c r="IN27" s="270"/>
+      <c r="IO27" s="257" t="s">
         <v>210</v>
       </c>
-      <c r="IP27" s="292"/>
-      <c r="IQ27" s="292"/>
-      <c r="IR27" s="292"/>
-      <c r="IS27" s="292"/>
-      <c r="IT27" s="292"/>
-      <c r="IU27" s="292"/>
-      <c r="IV27" s="292"/>
-      <c r="IW27" s="292"/>
-      <c r="IX27" s="292"/>
-      <c r="IY27" s="292"/>
-      <c r="IZ27" s="292"/>
-      <c r="JA27" s="292"/>
-      <c r="JB27" s="292"/>
-      <c r="JC27" s="292"/>
-      <c r="JD27" s="292"/>
-      <c r="JE27" s="292"/>
-      <c r="JF27" s="292"/>
+      <c r="IP27" s="257"/>
+      <c r="IQ27" s="257"/>
+      <c r="IR27" s="257"/>
+      <c r="IS27" s="257"/>
+      <c r="IT27" s="257"/>
+      <c r="IU27" s="257"/>
+      <c r="IV27" s="257"/>
+      <c r="IW27" s="257"/>
+      <c r="IX27" s="257"/>
+      <c r="IY27" s="257"/>
+      <c r="IZ27" s="257"/>
+      <c r="JA27" s="257"/>
+      <c r="JB27" s="257"/>
+      <c r="JC27" s="257"/>
+      <c r="JD27" s="257"/>
+      <c r="JE27" s="257"/>
+      <c r="JF27" s="257"/>
       <c r="JG27" s="214" t="s">
         <v>237</v>
       </c>
@@ -17459,19 +17473,43 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="IO27:JF27"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:AA26"/>
-    <mergeCell ref="AB26:AM26"/>
-    <mergeCell ref="AN26:BC26"/>
-    <mergeCell ref="HO27:HV27"/>
-    <mergeCell ref="BL26:BS26"/>
-    <mergeCell ref="BW26:CA26"/>
-    <mergeCell ref="EW26:EZ26"/>
-    <mergeCell ref="FK26:FO26"/>
-    <mergeCell ref="FQ27:FR27"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="Q9:T10"/>
+    <mergeCell ref="U9:V10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="Q4:V4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="K26:K27"/>
     <mergeCell ref="Q16:T16"/>
     <mergeCell ref="U16:V16"/>
     <mergeCell ref="EA26:EP26"/>
@@ -17488,157 +17526,133 @@
     <mergeCell ref="EQ26:EV26"/>
     <mergeCell ref="FA26:FD26"/>
     <mergeCell ref="FE26:FJ26"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="Q14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="Q12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="Q4:V4"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="Q9:T10"/>
-    <mergeCell ref="U9:V10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="IO27:JF27"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:AA26"/>
+    <mergeCell ref="AB26:AM26"/>
+    <mergeCell ref="AN26:BC26"/>
+    <mergeCell ref="HO27:HV27"/>
+    <mergeCell ref="BL26:BS26"/>
+    <mergeCell ref="BW26:CA26"/>
+    <mergeCell ref="EW26:EZ26"/>
+    <mergeCell ref="FK26:FO26"/>
+    <mergeCell ref="FQ27:FR27"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="Q28:T28">
-    <cfRule type="expression" dxfId="34" priority="100">
+    <cfRule type="expression" dxfId="32" priority="100">
       <formula>NOT(_xlfn.ISFORMULA(Q28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT28:AU28">
-    <cfRule type="expression" dxfId="33" priority="95">
+    <cfRule type="expression" dxfId="31" priority="95">
       <formula>NOT(_xlfn.ISFORMULA(AT28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX28:AY28">
-    <cfRule type="expression" dxfId="32" priority="97">
+    <cfRule type="expression" dxfId="30" priority="97">
       <formula>NOT(_xlfn.ISFORMULA(AX28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GC28 GF28:GG28">
-    <cfRule type="cellIs" dxfId="31" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="85" operator="equal">
       <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="86" operator="equal">
       <formula>"INTEGER_4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="87" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="88" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="89" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="90" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GK28">
-    <cfRule type="cellIs" dxfId="25" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="61" operator="equal">
       <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="62" operator="equal">
       <formula>"INTEGER_4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="63" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="64" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="65" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="66" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GN28">
-    <cfRule type="cellIs" dxfId="19" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="43" operator="equal">
       <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="44" operator="equal">
       <formula>"INTEGER_4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="45" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="46" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="47" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="48" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GP28:GR28">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
       <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"INTEGER_4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="22" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="24" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="GT28:HD28 HF28 HH28:HM28">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"INTEGER_5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"INTEGER_4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"INTEGER_3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"INTEGER_2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"INTEGER_1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"INTEGER_0"</formula>
     </cfRule>
   </conditionalFormatting>
